--- a/META_j.xlsx
+++ b/META_j.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffe\Documents\GitHub\martinshkreli-models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9164BF66-4113-4AE7-BF8C-C490A54A01E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC802F6-0395-475D-B970-E94BD67F88D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" activeTab="1" xr2:uid="{DF105585-55F7-489F-BFB3-1F48B85ABA8A}"/>
   </bookViews>
@@ -926,6 +926,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -998,12 +1001,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1056,8 +1060,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
@@ -1541,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="17">
-        <v>648.35</v>
+        <v>661.46</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -1555,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="3">
-        <v>2590</v>
+        <v>2609</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>215</v>
@@ -1573,7 +1579,7 @@
       </c>
       <c r="M4" s="3">
         <f>+M3*M2</f>
-        <v>1679226.5</v>
+        <v>1725749.1400000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1610,7 +1616,7 @@
       </c>
       <c r="M7" s="3">
         <f>+M4-M5+M6</f>
-        <v>1631657.5</v>
+        <v>1678180.1400000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1721,6 +1727,7 @@
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="38" width="8.85546875" style="1"/>
     <col min="39" max="61" width="9.140625" style="1"/>
+    <col min="106" max="106" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:99" x14ac:dyDescent="0.2">
@@ -4591,6 +4598,10 @@
       <c r="BQ29" s="3">
         <v>690</v>
       </c>
+      <c r="BR29" s="3">
+        <f>2584-SUM(BO29:BQ29)</f>
+        <v>801</v>
+      </c>
       <c r="CI29" s="3">
         <v>825</v>
       </c>
@@ -4614,6 +4625,10 @@
       <c r="CO29" s="3">
         <f>SUM(BK29:BN29)</f>
         <v>1722</v>
+      </c>
+      <c r="CP29" s="3">
+        <f>SUM(BO29:BR29)</f>
+        <v>2584</v>
       </c>
     </row>
     <row r="30" spans="2:104" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -4727,6 +4742,10 @@
       <c r="BQ30" s="3">
         <v>470</v>
       </c>
+      <c r="BR30" s="3">
+        <f>2207-SUM(BO30:BQ30)</f>
+        <v>955</v>
+      </c>
       <c r="CJ30" s="3">
         <v>501</v>
       </c>
@@ -4747,6 +4766,10 @@
       <c r="CO30" s="3">
         <f>SUM(BK30:BN30)</f>
         <v>2146</v>
+      </c>
+      <c r="CP30" s="3">
+        <f>SUM(BO30:BR30)</f>
+        <v>2207</v>
       </c>
     </row>
     <row r="31" spans="2:104" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -4928,7 +4951,10 @@
       <c r="BQ31" s="6">
         <v>50082</v>
       </c>
-      <c r="BR31" s="6"/>
+      <c r="BR31" s="6">
+        <f>196175-SUM(BO31:BQ31)</f>
+        <v>58138</v>
+      </c>
       <c r="BS31" s="6"/>
       <c r="BU31" s="3">
         <v>0.38200000000000001</v>
@@ -4998,6 +5024,10 @@
         <f>SUM(BK31:BN31)</f>
         <v>160632</v>
       </c>
+      <c r="CP31" s="3">
+        <f>SUM(BO31:BR31)</f>
+        <v>196175</v>
+      </c>
     </row>
     <row r="32" spans="2:104" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
@@ -5263,8 +5293,8 @@
         <v>51242</v>
       </c>
       <c r="BR32" s="8">
-        <f>(56000+59000)/2</f>
-        <v>57500</v>
+        <f>200966-SUM(BO32:BQ32)</f>
+        <v>59894</v>
       </c>
       <c r="BS32" s="8"/>
       <c r="BU32" s="7">
@@ -5353,47 +5383,47 @@
       </c>
       <c r="CP32" s="7">
         <f>SUM(BO32:BR32)</f>
-        <v>198572</v>
+        <v>200966</v>
       </c>
       <c r="CQ32" s="7">
         <f>+CP32*1.2</f>
-        <v>238286.4</v>
+        <v>241159.19999999998</v>
       </c>
       <c r="CR32" s="7">
         <f>+CQ32*1.18</f>
-        <v>281177.95199999999</v>
+        <v>284567.85599999997</v>
       </c>
       <c r="CS32" s="7">
         <f>+CR32*1.18</f>
-        <v>331789.98335999995</v>
+        <v>335790.07007999998</v>
       </c>
       <c r="CT32" s="7">
         <f>+CS32*1.15</f>
-        <v>381558.48086399992</v>
+        <v>386158.58059199993</v>
       </c>
       <c r="CU32" s="7">
         <f>+CT32*1.15</f>
-        <v>438792.25299359986</v>
+        <v>444082.36768079986</v>
       </c>
       <c r="CV32" s="7">
         <f>+CU32*1.1</f>
-        <v>482671.47829295986</v>
+        <v>488490.60444887989</v>
       </c>
       <c r="CW32" s="7">
         <f>+CV32*1.08</f>
-        <v>521285.19655639667</v>
+        <v>527569.85280479037</v>
       </c>
       <c r="CX32" s="7">
         <f>+CW32*1.08</f>
-        <v>562988.01228090841</v>
+        <v>569775.44102917367</v>
       </c>
       <c r="CY32" s="7">
         <f>CX32*1.05</f>
-        <v>591137.41289495386</v>
+        <v>598264.21308063238</v>
       </c>
       <c r="CZ32" s="7">
         <f>CY32*1.05</f>
-        <v>620694.2835397016</v>
+        <v>628177.42373466399</v>
       </c>
     </row>
     <row r="33" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5555,8 +5585,8 @@
         <v>9206</v>
       </c>
       <c r="BR33" s="6">
-        <f>+BR32-BR34</f>
-        <v>9775</v>
+        <f>36175-SUM(BO33:BQ33)</f>
+        <v>10906</v>
       </c>
       <c r="BS33" s="6"/>
       <c r="BX33" s="3">
@@ -5618,47 +5648,47 @@
       </c>
       <c r="CP33" s="3">
         <f t="shared" si="27"/>
-        <v>37728.679999999993</v>
+        <v>38183.539999999979</v>
       </c>
       <c r="CQ33" s="3">
         <f t="shared" si="27"/>
-        <v>45274.415999999997</v>
+        <v>45820.247999999992</v>
       </c>
       <c r="CR33" s="3">
         <f t="shared" si="27"/>
-        <v>53423.810879999975</v>
+        <v>54067.892639999976</v>
       </c>
       <c r="CS33" s="3">
         <f t="shared" si="27"/>
-        <v>63040.096838400001</v>
+        <v>63800.113315199967</v>
       </c>
       <c r="CT33" s="3">
         <f t="shared" si="27"/>
-        <v>72496.111364159966</v>
+        <v>73370.130312479974</v>
       </c>
       <c r="CU33" s="3">
         <f t="shared" si="27"/>
-        <v>83370.528068783926</v>
+        <v>84375.649859351921</v>
       </c>
       <c r="CV33" s="3">
         <f t="shared" si="27"/>
-        <v>91707.58087566233</v>
+        <v>92813.214845287148</v>
       </c>
       <c r="CW33" s="3">
         <f t="shared" si="27"/>
-        <v>99044.187345715356</v>
+        <v>100238.27203291014</v>
       </c>
       <c r="CX33" s="3">
         <f t="shared" si="27"/>
-        <v>106967.72233337257</v>
+        <v>108257.33379554295</v>
       </c>
       <c r="CY33" s="3">
         <f t="shared" si="27"/>
-        <v>112316.10845004121</v>
+        <v>113670.20048532012</v>
       </c>
       <c r="CZ33" s="3">
         <f t="shared" si="27"/>
-        <v>117931.91387254326</v>
+        <v>119353.71050958615</v>
       </c>
     </row>
     <row r="34" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5862,8 +5892,8 @@
         <v>42036</v>
       </c>
       <c r="BR34" s="6">
-        <f>+BR32*0.83</f>
-        <v>47725</v>
+        <f>BR32-BR33</f>
+        <v>48988</v>
       </c>
       <c r="BS34" s="6"/>
       <c r="BX34" s="3">
@@ -5940,47 +5970,47 @@
       </c>
       <c r="CP34" s="3">
         <f t="shared" si="40"/>
-        <v>160843.32</v>
+        <v>162782.46000000002</v>
       </c>
       <c r="CQ34" s="3">
         <f t="shared" si="40"/>
-        <v>193011.984</v>
+        <v>195338.95199999999</v>
       </c>
       <c r="CR34" s="3">
         <f t="shared" si="40"/>
-        <v>227754.14112000001</v>
+        <v>230499.96335999999</v>
       </c>
       <c r="CS34" s="3">
         <f t="shared" si="40"/>
-        <v>268749.88652159995</v>
+        <v>271989.95676480001</v>
       </c>
       <c r="CT34" s="3">
         <f t="shared" si="40"/>
-        <v>309062.36949983996</v>
+        <v>312788.45027951995</v>
       </c>
       <c r="CU34" s="3">
         <f t="shared" si="40"/>
-        <v>355421.72492481594</v>
+        <v>359706.71782144794</v>
       </c>
       <c r="CV34" s="3">
         <f t="shared" si="40"/>
-        <v>390963.89741729753</v>
+        <v>395677.38960359275</v>
       </c>
       <c r="CW34" s="3">
         <f t="shared" si="40"/>
-        <v>422241.00921068131</v>
+        <v>427331.58077188022</v>
       </c>
       <c r="CX34" s="3">
         <f t="shared" si="40"/>
-        <v>456020.28994753584</v>
+        <v>461518.10723363073</v>
       </c>
       <c r="CY34" s="3">
         <f t="shared" si="40"/>
-        <v>478821.30444491265</v>
+        <v>484594.01259531226</v>
       </c>
       <c r="CZ34" s="3">
         <f t="shared" si="40"/>
-        <v>502762.36966715835</v>
+        <v>508823.71322507784</v>
       </c>
     </row>
     <row r="35" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -6142,8 +6172,8 @@
         <v>15144</v>
       </c>
       <c r="BR35" s="6">
-        <f t="shared" ref="BQ35:BR36" si="41">+BN35</f>
-        <v>12180</v>
+        <f>57372-SUM(BO35:BQ35)</f>
+        <v>17136</v>
       </c>
       <c r="BS35" s="6"/>
       <c r="BX35" s="3">
@@ -6192,59 +6222,59 @@
         <v>24655</v>
       </c>
       <c r="CM35" s="3">
-        <f t="shared" ref="CM35:CR35" si="42">+CL35*0.9</f>
+        <f t="shared" ref="CM35:CR35" si="41">+CL35*0.9</f>
         <v>22189.5</v>
       </c>
       <c r="CN35" s="3">
+        <f t="shared" si="41"/>
+        <v>19970.55</v>
+      </c>
+      <c r="CO35" s="3">
+        <f t="shared" si="41"/>
+        <v>17973.494999999999</v>
+      </c>
+      <c r="CP35" s="3">
+        <f t="shared" si="41"/>
+        <v>16176.145499999999</v>
+      </c>
+      <c r="CQ35" s="3">
+        <f t="shared" si="41"/>
+        <v>14558.530949999998</v>
+      </c>
+      <c r="CR35" s="3">
+        <f t="shared" si="41"/>
+        <v>13102.677854999998</v>
+      </c>
+      <c r="CS35" s="3">
+        <f t="shared" ref="CS35:CU35" si="42">+CR35*0.9</f>
+        <v>11792.410069499998</v>
+      </c>
+      <c r="CT35" s="3">
         <f t="shared" si="42"/>
-        <v>19970.55</v>
-      </c>
-      <c r="CO35" s="3">
+        <v>10613.169062549998</v>
+      </c>
+      <c r="CU35" s="3">
         <f t="shared" si="42"/>
-        <v>17973.494999999999</v>
-      </c>
-      <c r="CP35" s="3">
-        <f t="shared" si="42"/>
-        <v>16176.145499999999</v>
-      </c>
-      <c r="CQ35" s="3">
-        <f t="shared" si="42"/>
-        <v>14558.530949999998</v>
-      </c>
-      <c r="CR35" s="3">
-        <f t="shared" si="42"/>
-        <v>13102.677854999998</v>
-      </c>
-      <c r="CS35" s="3">
-        <f t="shared" ref="CS35:CU35" si="43">+CR35*0.9</f>
-        <v>11792.410069499998</v>
-      </c>
-      <c r="CT35" s="3">
-        <f t="shared" si="43"/>
-        <v>10613.169062549998</v>
-      </c>
-      <c r="CU35" s="3">
-        <f t="shared" si="43"/>
         <v>9551.8521562949991</v>
       </c>
       <c r="CV35" s="3">
-        <f t="shared" ref="CV35" si="44">+CU35*0.9</f>
+        <f t="shared" ref="CV35" si="43">+CU35*0.9</f>
         <v>8596.6669406655001</v>
       </c>
       <c r="CW35" s="3">
-        <f t="shared" ref="CW35" si="45">+CV35*0.9</f>
+        <f t="shared" ref="CW35" si="44">+CV35*0.9</f>
         <v>7737.0002465989501</v>
       </c>
       <c r="CX35" s="3">
-        <f t="shared" ref="CX35" si="46">+CW35*0.9</f>
+        <f t="shared" ref="CX35" si="45">+CW35*0.9</f>
         <v>6963.3002219390555</v>
       </c>
       <c r="CY35" s="3">
-        <f t="shared" ref="CY35" si="47">+CX35*0.9</f>
+        <f t="shared" ref="CY35" si="46">+CX35*0.9</f>
         <v>6266.9701997451502</v>
       </c>
       <c r="CZ35" s="3">
-        <f t="shared" ref="CZ35" si="48">+CY35*0.9</f>
+        <f t="shared" ref="CZ35" si="47">+CY35*0.9</f>
         <v>5640.2731797706356</v>
       </c>
     </row>
@@ -6373,7 +6403,7 @@
         <v>4574</v>
       </c>
       <c r="BG36" s="6">
-        <f t="shared" ref="BG36:BG37" si="49">+BC36*0.9</f>
+        <f t="shared" ref="BG36:BG37" si="48">+BC36*0.9</f>
         <v>2980.8</v>
       </c>
       <c r="BH36" s="6">
@@ -6407,8 +6437,8 @@
         <v>2845</v>
       </c>
       <c r="BR36" s="6">
-        <f t="shared" si="41"/>
-        <v>3240</v>
+        <f>11911-SUM(BO36:BQ36)</f>
+        <v>3330</v>
       </c>
       <c r="BS36" s="6"/>
       <c r="BX36" s="3">
@@ -6461,55 +6491,55 @@
         <v>14043</v>
       </c>
       <c r="CN36" s="3">
-        <f t="shared" ref="CN36:CU36" si="50">+CM36</f>
+        <f t="shared" ref="CN36:CU36" si="49">+CM36</f>
         <v>14043</v>
       </c>
       <c r="CO36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CP36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CQ36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CR36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CS36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CT36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CU36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>14043</v>
       </c>
       <c r="CV36" s="3">
-        <f t="shared" ref="CV36:CV37" si="51">+CU36</f>
+        <f t="shared" ref="CV36:CV37" si="50">+CU36</f>
         <v>14043</v>
       </c>
       <c r="CW36" s="3">
-        <f t="shared" ref="CW36:CW37" si="52">+CV36</f>
+        <f t="shared" ref="CW36:CW37" si="51">+CV36</f>
         <v>14043</v>
       </c>
       <c r="CX36" s="3">
-        <f t="shared" ref="CX36:CX37" si="53">+CW36</f>
+        <f t="shared" ref="CX36:CX37" si="52">+CW36</f>
         <v>14043</v>
       </c>
       <c r="CY36" s="3">
-        <f t="shared" ref="CY36:CY37" si="54">+CX36</f>
+        <f t="shared" ref="CY36:CY37" si="53">+CX36</f>
         <v>14043</v>
       </c>
       <c r="CZ36" s="3">
-        <f t="shared" ref="CZ36:CZ37" si="55">+CY36</f>
+        <f t="shared" ref="CZ36:CZ37" si="54">+CY36</f>
         <v>14043</v>
       </c>
     </row>
@@ -6640,7 +6670,7 @@
         <v>3085</v>
       </c>
       <c r="BG37" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>2124</v>
       </c>
       <c r="BH37" s="6">
@@ -6675,8 +6705,8 @@
         <v>3512</v>
       </c>
       <c r="BR37" s="6">
-        <f>+BQ37</f>
-        <v>3512</v>
+        <f>12152-SUM(BO37:BQ37)</f>
+        <v>3697</v>
       </c>
       <c r="BS37" s="6"/>
       <c r="BX37" s="3">
@@ -6726,59 +6756,59 @@
         <v>9829</v>
       </c>
       <c r="CM37" s="3">
-        <f t="shared" ref="CM37:CU37" si="56">+CL37</f>
+        <f t="shared" ref="CM37:CU37" si="55">+CL37</f>
         <v>9829</v>
       </c>
       <c r="CN37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CO37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CP37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CQ37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CR37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CS37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CT37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CU37" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
       <c r="CV37" s="3">
+        <f t="shared" si="50"/>
+        <v>9829</v>
+      </c>
+      <c r="CW37" s="3">
         <f t="shared" si="51"/>
         <v>9829</v>
       </c>
-      <c r="CW37" s="3">
+      <c r="CX37" s="3">
         <f t="shared" si="52"/>
         <v>9829</v>
       </c>
-      <c r="CX37" s="3">
+      <c r="CY37" s="3">
         <f t="shared" si="53"/>
         <v>9829</v>
       </c>
-      <c r="CY37" s="3">
+      <c r="CZ37" s="3">
         <f t="shared" si="54"/>
-        <v>9829</v>
-      </c>
-      <c r="CZ37" s="3">
-        <f t="shared" si="55"/>
         <v>9829</v>
       </c>
     </row>
@@ -6791,47 +6821,47 @@
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6">
-        <f t="shared" ref="G38" si="57">SUM(G35:G37)</f>
+        <f t="shared" ref="G38" si="56">SUM(G35:G37)</f>
         <v>83</v>
       </c>
       <c r="H38" s="6">
-        <f t="shared" ref="H38" si="58">SUM(H35:H37)</f>
+        <f t="shared" ref="H38" si="57">SUM(H35:H37)</f>
         <v>102</v>
       </c>
       <c r="I38" s="6">
-        <f t="shared" ref="I38" si="59">SUM(I35:I37)</f>
+        <f t="shared" ref="I38" si="58">SUM(I35:I37)</f>
         <v>120</v>
       </c>
       <c r="J38" s="6">
-        <f t="shared" ref="J38:Q38" si="60">SUM(J35:J37)</f>
+        <f t="shared" ref="J38:Q38" si="59">SUM(J35:J37)</f>
         <v>144</v>
       </c>
       <c r="K38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>176</v>
       </c>
       <c r="L38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>278</v>
       </c>
       <c r="M38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>304</v>
       </c>
       <c r="N38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>336</v>
       </c>
       <c r="O38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>400</v>
       </c>
       <c r="P38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>1560</v>
       </c>
       <c r="Q38" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>563</v>
       </c>
       <c r="R38" s="6">
@@ -6859,67 +6889,67 @@
       <c r="AK38" s="6"/>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6">
-        <f t="shared" ref="AM38:AN38" si="61">+AM37+AM36+AM35</f>
+        <f t="shared" ref="AM38:AN38" si="60">+AM37+AM36+AM35</f>
         <v>4590</v>
       </c>
       <c r="AN38" s="6">
+        <f t="shared" si="60"/>
+        <v>5154</v>
+      </c>
+      <c r="AO38" s="6">
+        <f t="shared" ref="AO38:AQ38" si="61">+AO37+AO36+AO35</f>
+        <v>5528</v>
+      </c>
+      <c r="AP38" s="6">
         <f t="shared" si="61"/>
-        <v>5154</v>
-      </c>
-      <c r="AO38" s="6">
-        <f t="shared" ref="AO38:AQ38" si="62">+AO37+AO36+AO35</f>
-        <v>5528</v>
-      </c>
-      <c r="AP38" s="6">
+        <v>6298</v>
+      </c>
+      <c r="AQ38" s="6">
+        <f t="shared" si="61"/>
+        <v>5944</v>
+      </c>
+      <c r="AR38" s="6">
+        <f t="shared" ref="AR38:AS38" si="62">+AR37+AR36+AR35</f>
+        <v>6953</v>
+      </c>
+      <c r="AS38" s="6">
         <f t="shared" si="62"/>
-        <v>6298</v>
-      </c>
-      <c r="AQ38" s="6">
-        <f t="shared" si="62"/>
-        <v>5944</v>
-      </c>
-      <c r="AR38" s="6">
-        <f t="shared" ref="AR38:AS38" si="63">+AR37+AR36+AR35</f>
-        <v>6953</v>
-      </c>
-      <c r="AS38" s="6">
+        <v>7312</v>
+      </c>
+      <c r="AT38" s="6">
+        <f t="shared" ref="AT38:AU38" si="63">+AT37+AT36+AT35</f>
+        <v>8732</v>
+      </c>
+      <c r="AU38" s="6">
         <f t="shared" si="63"/>
-        <v>7312</v>
-      </c>
-      <c r="AT38" s="6">
-        <f t="shared" ref="AT38:AU38" si="64">+AT37+AT36+AT35</f>
-        <v>8732</v>
-      </c>
-      <c r="AU38" s="6">
-        <f t="shared" si="64"/>
         <v>8385</v>
       </c>
       <c r="AV38" s="6">
-        <f t="shared" ref="AV38" si="65">+AV37+AV36+AV35</f>
+        <f t="shared" ref="AV38" si="64">+AV37+AV36+AV35</f>
         <v>8895</v>
       </c>
       <c r="AW38" s="6">
-        <f t="shared" ref="AW38" si="66">+AW37+AW36+AW35</f>
+        <f t="shared" ref="AW38" si="65">+AW37+AW36+AW35</f>
         <v>9236</v>
       </c>
       <c r="AX38" s="6">
-        <f t="shared" ref="AX38" si="67">+AX37+AX36+AX35</f>
+        <f t="shared" ref="AX38" si="66">+AX37+AX36+AX35</f>
         <v>10087</v>
       </c>
       <c r="AY38" s="6">
-        <f t="shared" ref="AY38:BB38" si="68">+AY37+AY36+AY35</f>
+        <f t="shared" ref="AY38:BB38" si="67">+AY37+AY36+AY35</f>
         <v>9662</v>
       </c>
       <c r="AZ38" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>11311</v>
       </c>
       <c r="BA38" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>12816</v>
       </c>
       <c r="BB38" s="6">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>14738</v>
       </c>
       <c r="BC38" s="6">
@@ -6927,31 +6957,31 @@
         <v>13379</v>
       </c>
       <c r="BD38" s="6">
-        <f t="shared" ref="BD38:BF38" si="69">+BD37+BD36+BD35</f>
+        <f t="shared" ref="BD38:BF38" si="68">+BD37+BD36+BD35</f>
         <v>15272</v>
       </c>
       <c r="BE38" s="6">
+        <f t="shared" si="68"/>
+        <v>16334</v>
+      </c>
+      <c r="BF38" s="6">
+        <f t="shared" si="68"/>
+        <v>17430</v>
+      </c>
+      <c r="BG38" s="6">
+        <f t="shared" ref="BG38:BJ38" si="69">+BG37+BG36+BG35</f>
+        <v>12041.1</v>
+      </c>
+      <c r="BH38" s="6">
         <f t="shared" si="69"/>
-        <v>16334</v>
-      </c>
-      <c r="BF38" s="6">
+        <v>14792</v>
+      </c>
+      <c r="BI38" s="6">
         <f t="shared" si="69"/>
-        <v>17430</v>
-      </c>
-      <c r="BG38" s="6">
-        <f t="shared" ref="BG38:BJ38" si="70">+BG37+BG36+BG35</f>
-        <v>12041.1</v>
-      </c>
-      <c r="BH38" s="6">
-        <f t="shared" si="70"/>
-        <v>14792</v>
-      </c>
-      <c r="BI38" s="6">
-        <f t="shared" si="70"/>
         <v>14188</v>
       </c>
       <c r="BJ38" s="6">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>16032</v>
       </c>
       <c r="BK38" s="6">
@@ -6975,60 +7005,60 @@
         <v>17187</v>
       </c>
       <c r="BP38" s="6">
-        <f t="shared" ref="BP38:BR38" si="71">+BP37+BP36+BP35</f>
+        <f t="shared" ref="BP38:BR38" si="70">+BP37+BP36+BP35</f>
         <v>18584</v>
       </c>
       <c r="BQ38" s="6">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>21501</v>
       </c>
       <c r="BR38" s="6">
-        <f t="shared" si="71"/>
-        <v>18932</v>
+        <f t="shared" si="70"/>
+        <v>24163</v>
       </c>
       <c r="BS38" s="6"/>
       <c r="BX38" s="6">
-        <f t="shared" ref="BX38:BY38" si="72">+BX37+BX36+BX35</f>
+        <f t="shared" ref="BX38:BY38" si="71">+BX37+BX36+BX35</f>
         <v>236</v>
       </c>
       <c r="BY38" s="6">
+        <f t="shared" si="71"/>
+        <v>203</v>
+      </c>
+      <c r="BZ38" s="6">
+        <f t="shared" ref="BZ38:CA38" si="72">+BZ37+BZ36+BZ35</f>
+        <v>292</v>
+      </c>
+      <c r="CA38" s="6">
         <f t="shared" si="72"/>
-        <v>203</v>
-      </c>
-      <c r="BZ38" s="6">
-        <f t="shared" ref="BZ38:CA38" si="73">+BZ37+BZ36+BZ35</f>
-        <v>292</v>
-      </c>
-      <c r="CA38" s="6">
+        <v>449</v>
+      </c>
+      <c r="CB38" s="6">
+        <f t="shared" ref="CB38:CC38" si="73">+CB37+CB36+CB35</f>
+        <v>1095</v>
+      </c>
+      <c r="CC38" s="6">
         <f t="shared" si="73"/>
-        <v>449</v>
-      </c>
-      <c r="CB38" s="6">
-        <f t="shared" ref="CB38:CC38" si="74">+CB37+CB36+CB35</f>
-        <v>1095</v>
-      </c>
-      <c r="CC38" s="6">
+        <v>3187</v>
+      </c>
+      <c r="CD38" s="6">
+        <f t="shared" ref="CD38:CH38" si="74">+CD37+CD36+CD35</f>
+        <v>3193</v>
+      </c>
+      <c r="CE38" s="6">
         <f t="shared" si="74"/>
-        <v>3187</v>
-      </c>
-      <c r="CD38" s="6">
-        <f t="shared" ref="CD38:CH38" si="75">+CD37+CD36+CD35</f>
-        <v>3193</v>
-      </c>
-      <c r="CE38" s="6">
-        <f t="shared" si="75"/>
         <v>5319</v>
       </c>
       <c r="CF38" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>8836</v>
       </c>
       <c r="CG38" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>11422</v>
       </c>
       <c r="CH38" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>14996</v>
       </c>
       <c r="CI38" s="3">
@@ -7044,63 +7074,63 @@
         <v>36602</v>
       </c>
       <c r="CL38" s="3">
-        <f t="shared" ref="CL38" si="76">SUM(CL35:CL37)</f>
+        <f t="shared" ref="CL38" si="75">SUM(CL35:CL37)</f>
         <v>48527</v>
       </c>
       <c r="CM38" s="3">
-        <f t="shared" ref="CM38" si="77">SUM(CM35:CM37)</f>
+        <f t="shared" ref="CM38" si="76">SUM(CM35:CM37)</f>
         <v>46061.5</v>
       </c>
       <c r="CN38" s="3">
-        <f t="shared" ref="CN38" si="78">SUM(CN35:CN37)</f>
+        <f t="shared" ref="CN38" si="77">SUM(CN35:CN37)</f>
         <v>43842.55</v>
       </c>
       <c r="CO38" s="3">
-        <f t="shared" ref="CO38" si="79">SUM(CO35:CO37)</f>
+        <f t="shared" ref="CO38" si="78">SUM(CO35:CO37)</f>
         <v>41845.494999999995</v>
       </c>
       <c r="CP38" s="3">
-        <f t="shared" ref="CP38" si="80">SUM(CP35:CP37)</f>
+        <f t="shared" ref="CP38" si="79">SUM(CP35:CP37)</f>
         <v>40048.145499999999</v>
       </c>
       <c r="CQ38" s="3">
-        <f t="shared" ref="CQ38" si="81">SUM(CQ35:CQ37)</f>
+        <f t="shared" ref="CQ38" si="80">SUM(CQ35:CQ37)</f>
         <v>38430.53095</v>
       </c>
       <c r="CR38" s="3">
-        <f t="shared" ref="CR38" si="82">SUM(CR35:CR37)</f>
+        <f t="shared" ref="CR38" si="81">SUM(CR35:CR37)</f>
         <v>36974.677855000002</v>
       </c>
       <c r="CS38" s="3">
-        <f t="shared" ref="CS38" si="83">SUM(CS35:CS37)</f>
+        <f t="shared" ref="CS38" si="82">SUM(CS35:CS37)</f>
         <v>35664.410069499994</v>
       </c>
       <c r="CT38" s="3">
-        <f t="shared" ref="CT38" si="84">SUM(CT35:CT37)</f>
+        <f t="shared" ref="CT38" si="83">SUM(CT35:CT37)</f>
         <v>34485.169062549998</v>
       </c>
       <c r="CU38" s="3">
-        <f t="shared" ref="CU38:CZ38" si="85">SUM(CU35:CU37)</f>
+        <f t="shared" ref="CU38:CZ38" si="84">SUM(CU35:CU37)</f>
         <v>33423.852156294997</v>
       </c>
       <c r="CV38" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>32468.666940665498</v>
       </c>
       <c r="CW38" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>31609.000246598949</v>
       </c>
       <c r="CX38" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>30835.300221939055</v>
       </c>
       <c r="CY38" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>30138.970199745148</v>
       </c>
       <c r="CZ38" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>29512.273179770636</v>
       </c>
     </row>
@@ -7113,47 +7143,47 @@
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6">
-        <f t="shared" ref="G39" si="86">+G34-G38</f>
+        <f t="shared" ref="G39" si="85">+G34-G38</f>
         <v>162</v>
       </c>
       <c r="H39" s="6">
-        <f t="shared" ref="H39" si="87">+H34-H38</f>
+        <f t="shared" ref="H39" si="86">+H34-H38</f>
         <v>219</v>
       </c>
       <c r="I39" s="6">
-        <f t="shared" ref="I39" si="88">+I34-I38</f>
+        <f t="shared" ref="I39" si="87">+I34-I38</f>
         <v>216</v>
       </c>
       <c r="J39" s="6">
-        <f t="shared" ref="J39:Q39" si="89">+J34-J38</f>
+        <f t="shared" ref="J39:Q39" si="88">+J34-J38</f>
         <v>437</v>
       </c>
       <c r="K39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>388</v>
       </c>
       <c r="L39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>407</v>
       </c>
       <c r="M39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>414</v>
       </c>
       <c r="N39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>548</v>
       </c>
       <c r="O39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>381</v>
       </c>
       <c r="P39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>-743</v>
       </c>
       <c r="Q39" s="6">
-        <f t="shared" si="89"/>
+        <f t="shared" si="88"/>
         <v>377</v>
       </c>
       <c r="R39" s="6">
@@ -7181,67 +7211,67 @@
       <c r="AK39" s="6"/>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6">
-        <f t="shared" ref="AM39:AN39" si="90">+AM34-AM38</f>
+        <f t="shared" ref="AM39:AN39" si="89">+AM34-AM38</f>
         <v>5449</v>
       </c>
       <c r="AN39" s="6">
+        <f t="shared" si="89"/>
+        <v>5863</v>
+      </c>
+      <c r="AO39" s="6">
+        <f t="shared" ref="AO39:AQ39" si="90">+AO34-AO38</f>
+        <v>5781</v>
+      </c>
+      <c r="AP39" s="6">
         <f t="shared" si="90"/>
-        <v>5863</v>
-      </c>
-      <c r="AO39" s="6">
-        <f t="shared" ref="AO39:AQ39" si="91">+AO34-AO38</f>
-        <v>5781</v>
-      </c>
-      <c r="AP39" s="6">
+        <v>7820</v>
+      </c>
+      <c r="AQ39" s="6">
+        <f t="shared" si="90"/>
+        <v>6317</v>
+      </c>
+      <c r="AR39" s="6">
+        <f t="shared" ref="AR39:AS39" si="91">+AR34-AR38</f>
+        <v>6626</v>
+      </c>
+      <c r="AS39" s="6">
         <f t="shared" si="91"/>
-        <v>7820</v>
-      </c>
-      <c r="AQ39" s="6">
-        <f t="shared" si="91"/>
-        <v>6317</v>
-      </c>
-      <c r="AR39" s="6">
-        <f t="shared" ref="AR39:AS39" si="92">+AR34-AR38</f>
-        <v>6626</v>
-      </c>
-      <c r="AS39" s="6">
+        <v>7185</v>
+      </c>
+      <c r="AT39" s="6">
+        <f t="shared" ref="AT39:AU39" si="92">+AT34-AT38</f>
+        <v>8858</v>
+      </c>
+      <c r="AU39" s="6">
         <f t="shared" si="92"/>
-        <v>7185</v>
-      </c>
-      <c r="AT39" s="6">
-        <f t="shared" ref="AT39:AU39" si="93">+AT34-AT38</f>
-        <v>8858</v>
-      </c>
-      <c r="AU39" s="6">
-        <f t="shared" si="93"/>
         <v>5893</v>
       </c>
       <c r="AV39" s="6">
-        <f t="shared" ref="AV39" si="94">+AV34-AV38</f>
+        <f t="shared" ref="AV39" si="93">+AV34-AV38</f>
         <v>5963</v>
       </c>
       <c r="AW39" s="6">
-        <f t="shared" ref="AW39" si="95">+AW34-AW38</f>
+        <f t="shared" ref="AW39" si="94">+AW34-AW38</f>
         <v>8040</v>
       </c>
       <c r="AX39" s="6">
-        <f t="shared" ref="AX39" si="96">+AX34-AX38</f>
+        <f t="shared" ref="AX39" si="95">+AX34-AX38</f>
         <v>12775</v>
       </c>
       <c r="AY39" s="6">
-        <f t="shared" ref="AY39:BB39" si="97">+AY34-AY38</f>
+        <f t="shared" ref="AY39:BB39" si="96">+AY34-AY38</f>
         <v>11378</v>
       </c>
       <c r="AZ39" s="6">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>12367</v>
       </c>
       <c r="BA39" s="6">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>10423</v>
       </c>
       <c r="BB39" s="6">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>12585</v>
       </c>
       <c r="BC39" s="6">
@@ -7249,31 +7279,31 @@
         <v>8524</v>
       </c>
       <c r="BD39" s="6">
-        <f t="shared" ref="BD39:BF39" si="98">+BD34-BD38</f>
+        <f t="shared" ref="BD39:BF39" si="97">+BD34-BD38</f>
         <v>8358</v>
       </c>
       <c r="BE39" s="6">
+        <f t="shared" si="97"/>
+        <v>5664</v>
+      </c>
+      <c r="BF39" s="6">
+        <f t="shared" si="97"/>
+        <v>6399</v>
+      </c>
+      <c r="BG39" s="6">
+        <f t="shared" ref="BG39:BJ39" si="98">+BG34-BG38</f>
+        <v>10588.449999999999</v>
+      </c>
+      <c r="BH39" s="6">
         <f t="shared" si="98"/>
-        <v>5664</v>
-      </c>
-      <c r="BF39" s="6">
+        <v>11262</v>
+      </c>
+      <c r="BI39" s="6">
         <f t="shared" si="98"/>
-        <v>6399</v>
-      </c>
-      <c r="BG39" s="6">
-        <f t="shared" ref="BG39:BJ39" si="99">+BG34-BG38</f>
-        <v>10588.449999999999</v>
-      </c>
-      <c r="BH39" s="6">
-        <f t="shared" si="99"/>
-        <v>11262</v>
-      </c>
-      <c r="BI39" s="6">
-        <f t="shared" si="99"/>
         <v>13748</v>
       </c>
       <c r="BJ39" s="6">
-        <f t="shared" si="99"/>
+        <f t="shared" si="98"/>
         <v>15655.690000000002</v>
       </c>
       <c r="BK39" s="6">
@@ -7297,60 +7327,60 @@
         <v>17555</v>
       </c>
       <c r="BP39" s="6">
-        <f t="shared" ref="BP39:BR39" si="100">+BP34-BP38</f>
+        <f t="shared" ref="BP39:BR39" si="99">+BP34-BP38</f>
         <v>20441</v>
       </c>
       <c r="BQ39" s="6">
-        <f t="shared" si="100"/>
+        <f t="shared" si="99"/>
         <v>20535</v>
       </c>
       <c r="BR39" s="6">
-        <f t="shared" si="100"/>
-        <v>28793</v>
+        <f t="shared" si="99"/>
+        <v>24825</v>
       </c>
       <c r="BS39" s="6"/>
       <c r="BX39" s="6">
-        <f t="shared" ref="BX39:BY39" si="101">+BX34-BX38</f>
+        <f t="shared" ref="BX39:BY39" si="100">+BX34-BX38</f>
         <v>-124</v>
       </c>
       <c r="BY39" s="6">
+        <f t="shared" si="100"/>
+        <v>-55</v>
+      </c>
+      <c r="BZ39" s="6">
+        <f t="shared" ref="BZ39:CA39" si="101">+BZ34-BZ38</f>
+        <v>262</v>
+      </c>
+      <c r="CA39" s="6">
         <f t="shared" si="101"/>
-        <v>-55</v>
-      </c>
-      <c r="BZ39" s="6">
-        <f t="shared" ref="BZ39:CA39" si="102">+BZ34-BZ38</f>
-        <v>262</v>
-      </c>
-      <c r="CA39" s="6">
+        <v>1032</v>
+      </c>
+      <c r="CB39" s="6">
+        <f t="shared" ref="CB39:CC39" si="102">+CB34-CB38</f>
+        <v>1756</v>
+      </c>
+      <c r="CC39" s="6">
         <f t="shared" si="102"/>
-        <v>1032</v>
-      </c>
-      <c r="CB39" s="6">
-        <f t="shared" ref="CB39:CC39" si="103">+CB34-CB38</f>
-        <v>1756</v>
-      </c>
-      <c r="CC39" s="6">
+        <v>538</v>
+      </c>
+      <c r="CD39" s="6">
+        <f t="shared" ref="CD39:CH39" si="103">+CD34-CD38</f>
+        <v>2804</v>
+      </c>
+      <c r="CE39" s="6">
         <f t="shared" si="103"/>
-        <v>538</v>
-      </c>
-      <c r="CD39" s="6">
-        <f t="shared" ref="CD39:CH39" si="104">+CD34-CD38</f>
-        <v>2804</v>
-      </c>
-      <c r="CE39" s="6">
-        <f t="shared" si="104"/>
         <v>4994</v>
       </c>
       <c r="CF39" s="6">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>6225</v>
       </c>
       <c r="CG39" s="6">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>12427</v>
       </c>
       <c r="CH39" s="6">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>20203</v>
       </c>
       <c r="CI39" s="3">
@@ -7366,64 +7396,64 @@
         <v>32671</v>
       </c>
       <c r="CL39" s="3">
-        <f t="shared" ref="CL39" si="105">CL34-CL38</f>
+        <f t="shared" ref="CL39" si="104">CL34-CL38</f>
         <v>46753</v>
       </c>
       <c r="CM39" s="3">
-        <f t="shared" ref="CM39" si="106">CM34-CM38</f>
+        <f t="shared" ref="CM39" si="105">CM34-CM38</f>
         <v>48391.790000000008</v>
       </c>
       <c r="CN39" s="3">
-        <f t="shared" ref="CN39" si="107">CN34-CN38</f>
+        <f t="shared" ref="CN39" si="106">CN34-CN38</f>
         <v>65427.260000000009</v>
       </c>
       <c r="CO39" s="3">
-        <f t="shared" ref="CO39" si="108">CO34-CO38</f>
+        <f t="shared" ref="CO39" si="107">CO34-CO38</f>
         <v>91399.505000000005</v>
       </c>
       <c r="CP39" s="3">
-        <f t="shared" ref="CP39" si="109">CP34-CP38</f>
-        <v>120795.17450000001</v>
+        <f t="shared" ref="CP39" si="108">CP34-CP38</f>
+        <v>122734.31450000002</v>
       </c>
       <c r="CQ39" s="3">
-        <f t="shared" ref="CQ39" si="110">CQ34-CQ38</f>
-        <v>154581.45305000001</v>
+        <f t="shared" ref="CQ39" si="109">CQ34-CQ38</f>
+        <v>156908.42105</v>
       </c>
       <c r="CR39" s="3">
-        <f t="shared" ref="CR39" si="111">CR34-CR38</f>
-        <v>190779.46326500003</v>
+        <f t="shared" ref="CR39" si="110">CR34-CR38</f>
+        <v>193525.28550499998</v>
       </c>
       <c r="CS39" s="3">
-        <f t="shared" ref="CS39" si="112">CS34-CS38</f>
-        <v>233085.47645209997</v>
+        <f t="shared" ref="CS39" si="111">CS34-CS38</f>
+        <v>236325.54669530003</v>
       </c>
       <c r="CT39" s="3">
-        <f t="shared" ref="CT39" si="113">CT34-CT38</f>
-        <v>274577.20043728995</v>
+        <f t="shared" ref="CT39" si="112">CT34-CT38</f>
+        <v>278303.28121696995</v>
       </c>
       <c r="CU39" s="3">
-        <f t="shared" ref="CU39:CZ39" si="114">CU34-CU38</f>
-        <v>321997.87276852096</v>
+        <f t="shared" ref="CU39:CZ39" si="113">CU34-CU38</f>
+        <v>326282.86566515296</v>
       </c>
       <c r="CV39" s="3">
-        <f t="shared" si="114"/>
-        <v>358495.23047663202</v>
+        <f t="shared" si="113"/>
+        <v>363208.72266292723</v>
       </c>
       <c r="CW39" s="3">
-        <f t="shared" si="114"/>
-        <v>390632.00896408234</v>
+        <f t="shared" si="113"/>
+        <v>395722.58052528126</v>
       </c>
       <c r="CX39" s="3">
-        <f t="shared" si="114"/>
-        <v>425184.9897255968</v>
+        <f t="shared" si="113"/>
+        <v>430682.80701169168</v>
       </c>
       <c r="CY39" s="3">
-        <f t="shared" si="114"/>
-        <v>448682.3342451675</v>
+        <f t="shared" si="113"/>
+        <v>454455.04239556711</v>
       </c>
       <c r="CZ39" s="3">
-        <f t="shared" si="114"/>
-        <v>473250.09648738772</v>
+        <f t="shared" si="113"/>
+        <v>479311.44004530722</v>
       </c>
     </row>
     <row r="40" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -7561,8 +7591,8 @@
         <v>1128</v>
       </c>
       <c r="BR40" s="6">
-        <f>+BQ40</f>
-        <v>1128</v>
+        <f>2565-SUM(BO40:BQ40)</f>
+        <v>517</v>
       </c>
       <c r="BS40" s="6"/>
       <c r="CA40" s="3">
@@ -7605,56 +7635,56 @@
         <v>531</v>
       </c>
       <c r="CN40" s="3">
-        <f>+CM59*$DB$58</f>
+        <f t="shared" ref="CN40:CZ40" si="114">+CM59*$DB$58</f>
         <v>938.78</v>
       </c>
       <c r="CO40" s="3">
-        <f>+CN59*$DB$58</f>
+        <f t="shared" si="114"/>
         <v>2027.1830560000003</v>
       </c>
       <c r="CP40" s="3">
-        <f>+CO59*$DB$58</f>
+        <f t="shared" si="114"/>
         <v>3559.3807401184004</v>
       </c>
       <c r="CQ40" s="3">
-        <f>+CP59*$DB$58</f>
-        <v>5598.7954460563415</v>
+        <f t="shared" si="114"/>
+        <v>5630.5973420563432</v>
       </c>
       <c r="CR40" s="3">
-        <f>+CQ59*$DB$58</f>
-        <v>8225.7515213916668</v>
+        <f t="shared" si="114"/>
+        <v>8296.2372436860678</v>
       </c>
       <c r="CS40" s="3">
-        <f>+CR59*$DB$58</f>
-        <v>11489.437043888491</v>
+        <f t="shared" si="114"/>
+        <v>11606.110216764519</v>
       </c>
       <c r="CT40" s="3">
-        <f>+CS59*$DB$58</f>
-        <v>15500.4656252227</v>
+        <f t="shared" si="114"/>
+        <v>15672.189390122379</v>
       </c>
       <c r="CU40" s="3">
-        <f>+CT59*$DB$58</f>
-        <v>20257.739348647909</v>
+        <f t="shared" si="114"/>
+        <v>20493.387108078692</v>
       </c>
       <c r="CV40" s="3">
-        <f>+CU59*$DB$58</f>
-        <v>25870.73138736948</v>
+        <f t="shared" si="114"/>
+        <v>26180.517653559687</v>
       </c>
       <c r="CW40" s="3">
-        <f>+CV59*$DB$58</f>
-        <v>32174.333161939103</v>
+        <f t="shared" si="114"/>
+        <v>32566.501194750075</v>
       </c>
       <c r="CX40" s="3">
-        <f>+CW59*$DB$58</f>
-        <v>39108.357172805852</v>
+        <f t="shared" si="114"/>
+        <v>39590.44213495859</v>
       </c>
       <c r="CY40" s="3">
-        <f>+CX59*$DB$58</f>
-        <v>46722.768061939656</v>
+        <f t="shared" si="114"/>
+        <v>47302.923420963649</v>
       </c>
       <c r="CZ40" s="3">
-        <f>+CY59*$DB$58</f>
-        <v>54847.411739776209</v>
+        <f t="shared" si="114"/>
+        <v>55531.754060354753</v>
       </c>
     </row>
     <row r="41" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -7823,7 +7853,7 @@
       </c>
       <c r="BR41" s="6">
         <f t="shared" si="121"/>
-        <v>29921</v>
+        <v>25342</v>
       </c>
       <c r="BS41" s="6"/>
       <c r="BX41" s="3">
@@ -7900,47 +7930,47 @@
       </c>
       <c r="CP41" s="3">
         <f t="shared" ref="CP41" si="130">+CP39+CP40</f>
-        <v>124354.55524011841</v>
+        <v>126293.69524011842</v>
       </c>
       <c r="CQ41" s="3">
         <f t="shared" ref="CQ41" si="131">+CQ39+CQ40</f>
-        <v>160180.24849605636</v>
+        <v>162539.01839205634</v>
       </c>
       <c r="CR41" s="3">
         <f t="shared" ref="CR41" si="132">+CR39+CR40</f>
-        <v>199005.21478639171</v>
+        <v>201821.52274868605</v>
       </c>
       <c r="CS41" s="3">
         <f t="shared" ref="CS41" si="133">+CS39+CS40</f>
-        <v>244574.91349598847</v>
+        <v>247931.65691206456</v>
       </c>
       <c r="CT41" s="3">
         <f t="shared" ref="CT41" si="134">+CT39+CT40</f>
-        <v>290077.66606251267</v>
+        <v>293975.47060709231</v>
       </c>
       <c r="CU41" s="3">
         <f t="shared" ref="CU41:CZ41" si="135">+CU39+CU40</f>
-        <v>342255.61211716884</v>
+        <v>346776.25277323165</v>
       </c>
       <c r="CV41" s="3">
         <f t="shared" si="135"/>
-        <v>384365.96186400147</v>
+        <v>389389.24031648692</v>
       </c>
       <c r="CW41" s="3">
         <f t="shared" si="135"/>
-        <v>422806.34212602145</v>
+        <v>428289.08172003133</v>
       </c>
       <c r="CX41" s="3">
         <f t="shared" si="135"/>
-        <v>464293.34689840267</v>
+        <v>470273.24914665025</v>
       </c>
       <c r="CY41" s="3">
         <f t="shared" si="135"/>
-        <v>495405.10230710718</v>
+        <v>501757.96581653075</v>
       </c>
       <c r="CZ41" s="3">
         <f t="shared" si="135"/>
-        <v>528097.50822716393</v>
+        <v>534843.19410566194</v>
       </c>
     </row>
     <row r="42" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -8079,8 +8109,8 @@
         <v>18954</v>
       </c>
       <c r="BR42" s="6">
-        <f>+BR41*0.15</f>
-        <v>4488.1499999999996</v>
+        <f>25474-SUM(BO42:BQ42)</f>
+        <v>2585</v>
       </c>
       <c r="BS42" s="6"/>
       <c r="CA42" s="3">
@@ -8134,47 +8164,47 @@
       </c>
       <c r="CP42" s="3">
         <f t="shared" si="137"/>
-        <v>22383.819943221311</v>
+        <v>22732.865143221316</v>
       </c>
       <c r="CQ42" s="3">
         <f t="shared" si="137"/>
-        <v>28832.444729290142</v>
+        <v>29257.023310570141</v>
       </c>
       <c r="CR42" s="3">
         <f t="shared" si="137"/>
-        <v>35820.938661550506</v>
+        <v>36327.874094763487</v>
       </c>
       <c r="CS42" s="3">
         <f t="shared" si="137"/>
-        <v>44023.484429277923</v>
+        <v>44627.698244171617</v>
       </c>
       <c r="CT42" s="3">
         <f t="shared" si="137"/>
-        <v>52213.979891252275</v>
+        <v>52915.584709276613</v>
       </c>
       <c r="CU42" s="3">
         <f t="shared" si="137"/>
-        <v>61606.010181090387</v>
+        <v>62419.725499181695</v>
       </c>
       <c r="CV42" s="3">
         <f t="shared" ref="CV42:CZ42" si="138">+CV41*0.18</f>
-        <v>69185.873135520262</v>
+        <v>70090.063256967638</v>
       </c>
       <c r="CW42" s="3">
         <f t="shared" si="138"/>
-        <v>76105.141582683864</v>
+        <v>77092.034709605636</v>
       </c>
       <c r="CX42" s="3">
         <f t="shared" si="138"/>
-        <v>83572.802441712483</v>
+        <v>84649.184846397038</v>
       </c>
       <c r="CY42" s="3">
         <f t="shared" si="138"/>
-        <v>89172.918415279288</v>
+        <v>90316.433846975531</v>
       </c>
       <c r="CZ42" s="3">
         <f t="shared" si="138"/>
-        <v>95057.55148088951</v>
+        <v>96271.774939019146</v>
       </c>
     </row>
     <row r="43" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -8343,7 +8373,7 @@
       </c>
       <c r="BR43" s="6">
         <f t="shared" si="146"/>
-        <v>25432.85</v>
+        <v>22757</v>
       </c>
       <c r="BS43" s="6"/>
       <c r="BX43" s="3">
@@ -8420,251 +8450,251 @@
       </c>
       <c r="CP43" s="3">
         <f t="shared" ref="CP43" si="154">+CP41-CP42</f>
-        <v>101970.7352968971</v>
+        <v>103560.83009689712</v>
       </c>
       <c r="CQ43" s="3">
         <f t="shared" ref="CQ43" si="155">+CQ41-CQ42</f>
-        <v>131347.80376676621</v>
+        <v>133281.99508148621</v>
       </c>
       <c r="CR43" s="3">
         <f t="shared" ref="CR43" si="156">+CR41-CR42</f>
-        <v>163184.27612484118</v>
+        <v>165493.64865392257</v>
       </c>
       <c r="CS43" s="3">
         <f t="shared" ref="CS43" si="157">+CS41-CS42</f>
-        <v>200551.42906671055</v>
+        <v>203303.95866789293</v>
       </c>
       <c r="CT43" s="3">
         <f t="shared" ref="CT43" si="158">+CT41-CT42</f>
-        <v>237863.6861712604</v>
+        <v>241059.88589781569</v>
       </c>
       <c r="CU43" s="3">
         <f t="shared" ref="CU43:CZ43" si="159">+CU41-CU42</f>
-        <v>280649.60193607846</v>
+        <v>284356.52727404993</v>
       </c>
       <c r="CV43" s="3">
         <f t="shared" si="159"/>
-        <v>315180.08872848121</v>
+        <v>319299.17705951928</v>
       </c>
       <c r="CW43" s="3">
         <f t="shared" si="159"/>
-        <v>346701.20054333762</v>
+        <v>351197.04701042571</v>
       </c>
       <c r="CX43" s="3">
         <f t="shared" si="159"/>
-        <v>380720.5444566902</v>
+        <v>385624.06430025323</v>
       </c>
       <c r="CY43" s="3">
         <f t="shared" si="159"/>
-        <v>406232.18389182788</v>
+        <v>411441.53196955519</v>
       </c>
       <c r="CZ43" s="3">
         <f t="shared" si="159"/>
-        <v>433039.95674627443</v>
+        <v>438571.41916664282</v>
       </c>
       <c r="DA43" s="3">
-        <f>+CZ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" ref="DA43:EF43" si="160">+CZ43*(1+$DB$57)</f>
+        <v>438571.41916664282</v>
       </c>
       <c r="DB43" s="3">
-        <f>+DA43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DC43" s="3">
-        <f>+DB43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DD43" s="3">
-        <f>+DC43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DE43" s="3">
-        <f>+DD43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DF43" s="3">
-        <f>+DE43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DG43" s="3">
-        <f>+DF43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DH43" s="3">
-        <f>+DG43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DI43" s="3">
-        <f>+DH43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DJ43" s="3">
-        <f>+DI43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DK43" s="3">
-        <f>+DJ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DL43" s="3">
-        <f>+DK43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DM43" s="3">
-        <f>+DL43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DN43" s="3">
-        <f>+DM43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DO43" s="3">
-        <f>+DN43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DP43" s="3">
-        <f>+DO43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DQ43" s="3">
-        <f>+DP43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DR43" s="3">
-        <f>+DQ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DS43" s="3">
-        <f>+DR43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DT43" s="3">
-        <f>+DS43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DU43" s="3">
-        <f>+DT43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DV43" s="3">
-        <f>+DU43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DW43" s="3">
-        <f>+DV43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DX43" s="3">
-        <f>+DW43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DY43" s="3">
-        <f>+DX43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="DZ43" s="3">
-        <f>+DY43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EA43" s="3">
-        <f>+DZ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EB43" s="3">
-        <f>+EA43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EC43" s="3">
-        <f>+EB43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="ED43" s="3">
-        <f>+EC43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EE43" s="3">
-        <f>+ED43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EF43" s="3">
-        <f>+EE43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="160"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EG43" s="3">
-        <f>+EF43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" ref="EG43:EY43" si="161">+EF43*(1+$DB$57)</f>
+        <v>438571.41916664282</v>
       </c>
       <c r="EH43" s="3">
-        <f>+EG43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EI43" s="3">
-        <f>+EH43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EJ43" s="3">
-        <f>+EI43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EK43" s="3">
-        <f>+EJ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EL43" s="3">
-        <f>+EK43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EM43" s="3">
-        <f>+EL43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EN43" s="3">
-        <f>+EM43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EO43" s="3">
-        <f>+EN43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EP43" s="3">
-        <f>+EO43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EQ43" s="3">
-        <f>+EP43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="ER43" s="3">
-        <f>+EQ43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="ES43" s="3">
-        <f>+ER43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="ET43" s="3">
-        <f>+ES43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EU43" s="3">
-        <f>+ET43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EV43" s="3">
-        <f>+EU43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EW43" s="3">
-        <f>+EV43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EX43" s="3">
-        <f>+EW43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
       <c r="EY43" s="3">
-        <f>+EX43*(1+$DB$57)</f>
-        <v>433039.95674627443</v>
+        <f t="shared" si="161"/>
+        <v>438571.41916664282</v>
       </c>
     </row>
     <row r="44" spans="2:155" x14ac:dyDescent="0.2">
@@ -8708,67 +8738,67 @@
       <c r="AK44" s="9"/>
       <c r="AL44" s="9"/>
       <c r="AM44" s="9">
-        <f t="shared" ref="AM44:AN44" si="160">+AM43/AM45</f>
+        <f t="shared" ref="AM44:AN44" si="162">+AM43/AM45</f>
         <v>1.6933786078098472</v>
       </c>
       <c r="AN44" s="9">
-        <f t="shared" si="160"/>
+        <f t="shared" si="162"/>
         <v>1.7426621160409557</v>
       </c>
       <c r="AO44" s="9">
-        <f t="shared" ref="AO44:AQ44" si="161">+AO43/AO45</f>
+        <f t="shared" ref="AO44:AQ44" si="163">+AO43/AO45</f>
         <v>1.7634740817027119</v>
       </c>
       <c r="AP44" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>2.3846153846153846</v>
       </c>
       <c r="AQ44" s="9">
-        <f t="shared" si="161"/>
+        <f t="shared" si="163"/>
         <v>1.4980869565217392</v>
       </c>
       <c r="AR44" s="9">
-        <f t="shared" ref="AR44" si="162">+AR43/AR45</f>
+        <f t="shared" ref="AR44" si="164">+AR43/AR45</f>
         <v>1.6055652173913044</v>
       </c>
       <c r="AS44" s="9">
-        <f t="shared" ref="AS44:AT44" si="163">+AS43/AS45</f>
+        <f t="shared" ref="AS44:AT44" si="165">+AS43/AS45</f>
         <v>2.1193458594293668</v>
       </c>
       <c r="AT44" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="165"/>
         <v>2.559735283873215</v>
       </c>
       <c r="AU44" s="9">
-        <f t="shared" ref="AU44:AV44" si="164">+AU43/AU45</f>
+        <f t="shared" ref="AU44:AV44" si="166">+AU43/AU45</f>
         <v>1.7092050209205021</v>
       </c>
       <c r="AV44" s="9">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>1.7985411601250434</v>
       </c>
       <c r="AW44" s="9">
-        <f t="shared" ref="AW44:BB44" si="165">+AW43/AW45</f>
+        <f t="shared" ref="AW44:BB44" si="167">+AW43/AW45</f>
         <v>2.7139398132134209</v>
       </c>
       <c r="AX44" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.882006920415225</v>
       </c>
       <c r="AY44" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.2952810548230396</v>
       </c>
       <c r="AZ44" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.6127911018421965</v>
       </c>
       <c r="BA44" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.2158097236796084</v>
       </c>
       <c r="BB44" s="9">
-        <f t="shared" si="165"/>
+        <f t="shared" si="167"/>
         <v>3.6745266166488033</v>
       </c>
       <c r="BC44" s="9">
@@ -8776,170 +8806,170 @@
         <v>2.7224653537563821</v>
       </c>
       <c r="BD44" s="9">
-        <f t="shared" ref="BD44:BF44" si="166">+BD43/BD45</f>
+        <f t="shared" ref="BD44:BF44" si="168">+BD43/BD45</f>
         <v>2.4647991153704387</v>
       </c>
       <c r="BE44" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.6356531447711202</v>
       </c>
       <c r="BF44" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="168"/>
         <v>1.7621212121212122</v>
       </c>
       <c r="BG44" s="9">
-        <f t="shared" ref="BG44:BR44" si="167">+BG43/BG45</f>
+        <f t="shared" ref="BG44:BR44" si="169">+BG43/BG45</f>
         <v>3.1720244318181812</v>
       </c>
       <c r="BH44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>3.6975497702909648</v>
       </c>
       <c r="BI44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>4.3858386974630825</v>
       </c>
       <c r="BJ44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>5.0527338403041835</v>
       </c>
       <c r="BK44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>4.7119999999999997</v>
       </c>
       <c r="BL44" s="9">
-        <f t="shared" ref="BL44" si="168">+BL43/BL45</f>
+        <f t="shared" ref="BL44" si="170">+BL43/BL45</f>
         <v>5.1590038314176248</v>
       </c>
       <c r="BM44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>6.0338461538461541</v>
       </c>
       <c r="BN44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>8.0176991150442483</v>
       </c>
       <c r="BO44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>6.4262548262548265</v>
       </c>
       <c r="BP44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>7.1350194552529187</v>
       </c>
       <c r="BQ44" s="9">
-        <f t="shared" si="167"/>
+        <f t="shared" si="169"/>
         <v>1.0540856031128405</v>
       </c>
       <c r="BR44" s="9">
-        <f t="shared" si="167"/>
-        <v>9.8960505836575869</v>
+        <f t="shared" si="169"/>
+        <v>8.8411033411033415</v>
       </c>
       <c r="BS44" s="9"/>
       <c r="BZ44" s="17"/>
       <c r="CA44" s="17">
-        <f t="shared" ref="CA44:CK44" si="169">+CA43/CA45</f>
+        <f t="shared" ref="CA44:CK44" si="171">+CA43/CA45</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="CB44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.66312997347480107</v>
       </c>
       <c r="CC44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>2.4469067405355493E-2</v>
       </c>
       <c r="CD44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>0.59594755661501786</v>
       </c>
       <c r="CE44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>1.1036036036036037</v>
       </c>
       <c r="CF44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>1.2926743778478795</v>
       </c>
       <c r="CG44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>3.4929914529914532</v>
       </c>
       <c r="CH44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>5.4850243863516397</v>
       </c>
       <c r="CI44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>7.5696679219445393</v>
       </c>
       <c r="CJ44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>8.1658553546592483</v>
       </c>
       <c r="CK44" s="17">
-        <f t="shared" si="169"/>
+        <f t="shared" si="171"/>
         <v>10.092105263157896</v>
       </c>
       <c r="CL44" s="17">
-        <f t="shared" ref="CL44" si="170">+CL43/CL45</f>
+        <f t="shared" ref="CL44" si="172">+CL43/CL45</f>
         <v>13.770549143057012</v>
       </c>
       <c r="CM44" s="17">
-        <f t="shared" ref="CM44" si="171">+CM43/CM45</f>
+        <f t="shared" ref="CM44" si="173">+CM43/CM45</f>
         <v>14.721301354108704</v>
       </c>
       <c r="CN44" s="17">
-        <f t="shared" ref="CN44" si="172">+CN43/CN45</f>
+        <f t="shared" ref="CN44" si="174">+CN43/CN45</f>
         <v>20.189260916342057</v>
       </c>
       <c r="CO44" s="17">
-        <f t="shared" ref="CO44" si="173">+CO43/CO45</f>
+        <f t="shared" ref="CO44" si="175">+CO43/CO45</f>
         <v>29.369324978309372</v>
       </c>
       <c r="CP44" s="17">
-        <f t="shared" ref="CP44" si="174">+CP43/CP45</f>
-        <v>39.091713742341227</v>
+        <f t="shared" ref="CP44" si="176">+CP43/CP45</f>
+        <v>39.701295800995638</v>
       </c>
       <c r="CQ44" s="17">
-        <f t="shared" ref="CQ44" si="175">+CQ43/CQ45</f>
-        <v>50.35376797652529</v>
+        <f t="shared" ref="CQ44" si="177">+CQ43/CQ45</f>
+        <v>51.095263592672495</v>
       </c>
       <c r="CR44" s="17">
-        <f t="shared" ref="CR44" si="176">+CR43/CR45</f>
-        <v>62.55866441435353</v>
+        <f t="shared" ref="CR44" si="178">+CR43/CR45</f>
+        <v>63.4439902832749</v>
       </c>
       <c r="CS44" s="17">
-        <f t="shared" ref="CS44" si="177">+CS43/CS45</f>
-        <v>76.88381409496283</v>
+        <f t="shared" ref="CS44" si="179">+CS43/CS45</f>
+        <v>77.939029583244363</v>
       </c>
       <c r="CT44" s="17">
-        <f t="shared" ref="CT44" si="178">+CT43/CT45</f>
-        <v>91.187918792892617</v>
+        <f t="shared" ref="CT44" si="180">+CT43/CT45</f>
+        <v>92.413220585706611</v>
       </c>
       <c r="CU44" s="17">
-        <f t="shared" ref="CU44:CZ44" si="179">+CU43/CU45</f>
-        <v>107.59041669008182</v>
+        <f t="shared" ref="CU44:CZ44" si="181">+CU43/CU45</f>
+        <v>109.01151131840136</v>
       </c>
       <c r="CV44" s="17">
-        <f t="shared" si="179"/>
-        <v>120.82809611979344</v>
+        <f t="shared" si="181"/>
+        <v>122.40719841269667</v>
       </c>
       <c r="CW44" s="17">
-        <f t="shared" si="179"/>
-        <v>132.91209528209225</v>
+        <f t="shared" si="181"/>
+        <v>134.63563235975684</v>
       </c>
       <c r="CX44" s="17">
-        <f t="shared" si="179"/>
-        <v>145.95382191170796</v>
+        <f t="shared" si="181"/>
+        <v>147.83364550517663</v>
       </c>
       <c r="CY44" s="17">
-        <f t="shared" si="179"/>
-        <v>155.73401720982477</v>
+        <f t="shared" si="181"/>
+        <v>157.7310837529443</v>
       </c>
       <c r="CZ44" s="17">
-        <f t="shared" si="179"/>
-        <v>166.01110091864075</v>
+        <f t="shared" si="181"/>
+        <v>168.13165388792135</v>
       </c>
     </row>
     <row r="45" spans="2:155" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -9078,8 +9108,7 @@
         <v>2570</v>
       </c>
       <c r="BR45" s="6">
-        <f>+BQ45</f>
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="BS45" s="6"/>
       <c r="CA45" s="3">
@@ -9124,7 +9153,7 @@
         <v>2695.5</v>
       </c>
       <c r="CN45" s="3">
-        <f t="shared" ref="CN45:CU45" si="180">+CM45</f>
+        <f t="shared" ref="CN45:CU45" si="182">+CM45</f>
         <v>2695.5</v>
       </c>
       <c r="CO45" s="3">
@@ -9132,47 +9161,47 @@
         <v>2608.5</v>
       </c>
       <c r="CP45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CQ45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CR45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CS45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CT45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CU45" s="3">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>2608.5</v>
       </c>
       <c r="CV45" s="3">
-        <f t="shared" ref="CV45" si="181">+CU45</f>
+        <f t="shared" ref="CV45" si="183">+CU45</f>
         <v>2608.5</v>
       </c>
       <c r="CW45" s="3">
-        <f t="shared" ref="CW45" si="182">+CV45</f>
+        <f t="shared" ref="CW45" si="184">+CV45</f>
         <v>2608.5</v>
       </c>
       <c r="CX45" s="3">
-        <f t="shared" ref="CX45" si="183">+CW45</f>
+        <f t="shared" ref="CX45" si="185">+CW45</f>
         <v>2608.5</v>
       </c>
       <c r="CY45" s="3">
-        <f t="shared" ref="CY45" si="184">+CX45</f>
+        <f t="shared" ref="CY45" si="186">+CX45</f>
         <v>2608.5</v>
       </c>
       <c r="CZ45" s="3">
-        <f t="shared" ref="CZ45" si="185">+CY45</f>
+        <f t="shared" ref="CZ45" si="187">+CY45</f>
         <v>2608.5</v>
       </c>
     </row>
@@ -9224,23 +9253,23 @@
       <c r="AO47" s="12"/>
       <c r="AP47" s="12"/>
       <c r="AQ47" s="11">
-        <f t="shared" ref="AQ47:AU47" si="186">+AQ32/AM32-1</f>
+        <f t="shared" ref="AQ47:AU47" si="188">+AQ32/AM32-1</f>
         <v>0.25998662878154777</v>
       </c>
       <c r="AR47" s="11">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.2762451817700855</v>
       </c>
       <c r="AS47" s="11">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.2859328331026445</v>
       </c>
       <c r="AT47" s="11">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.2464230814709707</v>
       </c>
       <c r="AU47" s="11">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.17642767128739134</v>
       </c>
       <c r="AV47" s="11">
@@ -9264,11 +9293,11 @@
         <v>0.5560014983678494</v>
       </c>
       <c r="BA47" s="11">
-        <f t="shared" ref="BA47:BB47" si="187">+BA32/AW32-1</f>
+        <f t="shared" ref="BA47:BB47" si="189">+BA32/AW32-1</f>
         <v>0.35118770377270603</v>
       </c>
       <c r="BB47" s="11">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.19945141065830718</v>
       </c>
       <c r="BC47" s="11">
@@ -9284,7 +9313,7 @@
         <v>-4.4674250258531556E-2</v>
       </c>
       <c r="BF47" s="11">
-        <f t="shared" ref="BF47" si="188">+BF32/BB32-1</f>
+        <f t="shared" ref="BF47" si="190">+BF32/BB32-1</f>
         <v>-4.4726916337501144E-2</v>
       </c>
       <c r="BG47" s="11">
@@ -9292,31 +9321,31 @@
         <v>2.6408198366060009E-2</v>
       </c>
       <c r="BH47" s="11">
-        <f t="shared" ref="BH47" si="189">+BH32/BD32-1</f>
+        <f t="shared" ref="BH47" si="191">+BH32/BD32-1</f>
         <v>0.11022829782804799</v>
       </c>
       <c r="BI47" s="11">
-        <f t="shared" ref="BI47" si="190">+BI32/BE32-1</f>
+        <f t="shared" ref="BI47" si="192">+BI32/BE32-1</f>
         <v>0.23208486685429741</v>
       </c>
       <c r="BJ47" s="11">
-        <f t="shared" ref="BJ47" si="191">+BJ32/BF32-1</f>
+        <f t="shared" ref="BJ47" si="193">+BJ32/BF32-1</f>
         <v>0.24703870666873939</v>
       </c>
       <c r="BK47" s="11">
-        <f t="shared" ref="BK47:BR47" si="192">+BK32/BG32-1</f>
+        <f t="shared" ref="BK47:BR47" si="194">+BK32/BG32-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="BL47" s="11">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>0.2210069064658271</v>
       </c>
       <c r="BM47" s="11">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>0.18868974404029748</v>
       </c>
       <c r="BN47" s="11">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>0.20627757971628724</v>
       </c>
       <c r="BO47" s="11">
@@ -9324,72 +9353,72 @@
         <v>0.16071869428062002</v>
       </c>
       <c r="BP47" s="11">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>0.21614496685521223</v>
       </c>
       <c r="BQ47" s="11">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>0.26246027248761972</v>
       </c>
       <c r="BR47" s="11">
-        <f t="shared" si="192"/>
-        <v>0.18838483000930051</v>
+        <f t="shared" si="194"/>
+        <v>0.23786297406220935</v>
       </c>
       <c r="BS47" s="11"/>
       <c r="BV47" s="18">
-        <f t="shared" ref="BV47:CH47" si="193">+BV32/BU32-1</f>
+        <f t="shared" ref="BV47:CH47" si="195">+BV32/BU32-1</f>
         <v>22.560209424083769</v>
       </c>
       <c r="BW47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>4.333333333333333</v>
       </c>
       <c r="BX47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>2.1875</v>
       </c>
       <c r="BY47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.77777777777777768</v>
       </c>
       <c r="BZ47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>1.8566176470588234</v>
       </c>
       <c r="CA47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>1.5405405405405403</v>
       </c>
       <c r="CB47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.87993920972644379</v>
       </c>
       <c r="CC47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.37132848288870934</v>
       </c>
       <c r="CD47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.5468657889565729</v>
       </c>
       <c r="CE47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.58358739837398366</v>
       </c>
       <c r="CF47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.43815177282207607</v>
       </c>
       <c r="CG47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.54161088799643009</v>
       </c>
       <c r="CH47" s="18">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>0.47090961719371882</v>
       </c>
       <c r="CI47" s="18">
-        <f t="shared" ref="CI47" si="194">+CI32/CH32-1</f>
+        <f t="shared" ref="CI47" si="196">+CI32/CH32-1</f>
         <v>0.37352716896661997</v>
       </c>
       <c r="CJ47" s="18">
@@ -9409,35 +9438,35 @@
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="CN47" s="18">
-        <f t="shared" ref="CN47:CU47" si="195">+CN32/CM32-1</f>
+        <f t="shared" ref="CN47:CU47" si="197">+CN32/CM32-1</f>
         <v>0.15686610810486323</v>
       </c>
       <c r="CO47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.21941275453851339</v>
       </c>
       <c r="CP47" s="18">
-        <f t="shared" si="195"/>
-        <v>0.20712462006079035</v>
+        <f t="shared" si="197"/>
+        <v>0.22167781155015187</v>
       </c>
       <c r="CQ47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="CR47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="CS47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="CT47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="CU47" s="18">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
@@ -9498,15 +9527,15 @@
         <v>0.41985917173887088</v>
       </c>
       <c r="AZ48" s="11">
-        <f t="shared" ref="AZ48:BB48" si="196">+AZ27/AV27-1</f>
+        <f t="shared" ref="AZ48:BB48" si="198">+AZ27/AV27-1</f>
         <v>0.47543879015343848</v>
       </c>
       <c r="BA48" s="11">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>0.31097316780136164</v>
       </c>
       <c r="BB48" s="11">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>0.14539923954372624</v>
       </c>
       <c r="BC48" s="11">
@@ -9518,7 +9547,7 @@
         <v>-1</v>
       </c>
       <c r="BE48" s="11">
-        <f t="shared" ref="BE48" si="197">+BE27/BA27-1</f>
+        <f t="shared" ref="BE48" si="199">+BE27/BA27-1</f>
         <v>-1</v>
       </c>
       <c r="BF48" s="11"/>
@@ -9724,76 +9753,76 @@
       <c r="AZ51" s="10"/>
       <c r="BA51" s="10"/>
       <c r="BB51" s="10">
-        <f t="shared" ref="BB51" si="198">+BB30/AX30-1</f>
+        <f t="shared" ref="BB51" si="200">+BB30/AX30-1</f>
         <v>0.22315202231520215</v>
       </c>
       <c r="BC51" s="10">
-        <f t="shared" ref="BC51:BK51" si="199">+BC30/AY30-1</f>
+        <f t="shared" ref="BC51:BK51" si="201">+BC30/AY30-1</f>
         <v>0.30149812734082393</v>
       </c>
       <c r="BD51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>0.4819672131147541</v>
       </c>
       <c r="BE51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>-0.489247311827957</v>
       </c>
       <c r="BF51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>-0.17103762827822122</v>
       </c>
       <c r="BG51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>-0.51223021582733819</v>
       </c>
       <c r="BH51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>-0.38938053097345138</v>
       </c>
       <c r="BI51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>-0.26315789473684215</v>
       </c>
       <c r="BJ51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>0.47317744154057761</v>
       </c>
       <c r="BK51" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>0.29793510324483785</v>
       </c>
       <c r="BL51" s="10">
-        <f t="shared" ref="BL51" si="200">+BL30/BH30-1</f>
+        <f t="shared" ref="BL51" si="202">+BL30/BH30-1</f>
         <v>0.27898550724637672</v>
       </c>
       <c r="BM51" s="10">
-        <f t="shared" ref="BM51" si="201">+BM30/BI30-1</f>
+        <f t="shared" ref="BM51" si="203">+BM30/BI30-1</f>
         <v>0.28571428571428581</v>
       </c>
       <c r="BN51" s="10">
-        <f t="shared" ref="BN51" si="202">+BN30/BJ30-1</f>
+        <f t="shared" ref="BN51" si="204">+BN30/BJ30-1</f>
         <v>1.1204481792717047E-2</v>
       </c>
       <c r="BO51" s="10">
-        <f t="shared" ref="BO51" si="203">+BO30/BK30-1</f>
+        <f t="shared" ref="BO51" si="205">+BO30/BK30-1</f>
         <v>-6.3636363636363602E-2</v>
       </c>
       <c r="BP51" s="10">
-        <f t="shared" ref="BP51" si="204">+BP30/BL30-1</f>
+        <f t="shared" ref="BP51" si="206">+BP30/BL30-1</f>
         <v>4.8158640226628968E-2</v>
       </c>
       <c r="BQ51" s="10">
-        <f t="shared" ref="BQ51" si="205">+BQ30/BM30-1</f>
+        <f t="shared" ref="BQ51" si="207">+BQ30/BM30-1</f>
         <v>0.7407407407407407</v>
       </c>
       <c r="BR51" s="10">
-        <f t="shared" ref="BR51" si="206">+BR30/BN30-1</f>
-        <v>-1</v>
+        <f t="shared" ref="BR51" si="208">+BR30/BN30-1</f>
+        <v>-0.11819021237303784</v>
       </c>
       <c r="BS51" s="10"/>
       <c r="CK51" s="19">
-        <f t="shared" ref="CK51" si="207">CK30/CJ30-1</f>
+        <f t="shared" ref="CK51" si="209">CK30/CJ30-1</f>
         <v>1.2734530938123751</v>
       </c>
       <c r="CL51" s="19">
@@ -9860,19 +9889,19 @@
       <c r="AY52" s="6"/>
       <c r="AZ52" s="6"/>
       <c r="BA52" s="10">
-        <f t="shared" ref="BA52:BD52" si="208">+BA38/AW38-1</f>
+        <f t="shared" ref="BA52:BD52" si="210">+BA38/AW38-1</f>
         <v>0.38761368557817244</v>
       </c>
       <c r="BB52" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.46108852979081982</v>
       </c>
       <c r="BC52" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.38470296004967919</v>
       </c>
       <c r="BD52" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="210"/>
         <v>0.35019008045265676</v>
       </c>
       <c r="BE52" s="10">
@@ -9880,23 +9909,23 @@
         <v>0.27450062421972543</v>
       </c>
       <c r="BF52" s="10">
-        <f t="shared" ref="BF52:BJ52" si="209">+BF38/BB38-1</f>
+        <f t="shared" ref="BF52:BJ52" si="211">+BF38/BB38-1</f>
         <v>0.18265707694395439</v>
       </c>
       <c r="BG52" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="BH52" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>-3.1430068098480923E-2</v>
       </c>
       <c r="BI52" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>-0.13138239255540585</v>
       </c>
       <c r="BJ52" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="211"/>
         <v>-8.0206540447504304E-2</v>
       </c>
       <c r="BK52" s="10">
@@ -9904,32 +9933,32 @@
         <v>0.32853310744035014</v>
       </c>
       <c r="BL52" s="10">
-        <f t="shared" ref="BL52:BO52" si="210">+BL38/BH38-1</f>
+        <f t="shared" ref="BL52:BO52" si="212">+BL38/BH38-1</f>
         <v>0.14359113034072468</v>
       </c>
       <c r="BM52" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>0.11812799548914565</v>
       </c>
       <c r="BN52" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>9.2939121756487886E-3</v>
       </c>
       <c r="BO52" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="212"/>
         <v>7.4388947927736426E-2</v>
       </c>
       <c r="BP52" s="10">
-        <f t="shared" ref="BP52" si="211">+BP38/BL38-1</f>
+        <f t="shared" ref="BP52" si="213">+BP38/BL38-1</f>
         <v>9.8604871127926152E-2</v>
       </c>
       <c r="BQ52" s="10">
-        <f t="shared" ref="BQ52" si="212">+BQ38/BM38-1</f>
+        <f t="shared" ref="BQ52" si="214">+BQ38/BM38-1</f>
         <v>0.35533282904689867</v>
       </c>
       <c r="BR52" s="10">
-        <f t="shared" ref="BR52" si="213">+BR38/BN38-1</f>
-        <v>0.17001421420184171</v>
+        <f t="shared" ref="BR52" si="215">+BR38/BN38-1</f>
+        <v>0.49329460478338794</v>
       </c>
       <c r="BS52" s="10"/>
     </row>
@@ -10045,99 +10074,99 @@
       <c r="AK54" s="10"/>
       <c r="AL54" s="10"/>
       <c r="AM54" s="10">
-        <f t="shared" ref="AM54:BJ54" si="214">+AM34/AM32</f>
+        <f t="shared" ref="AM54:BJ54" si="216">+AM34/AM32</f>
         <v>0.8389603877653351</v>
       </c>
       <c r="AN54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.83266570931902351</v>
       </c>
       <c r="AO54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.82385080498288044</v>
       </c>
       <c r="AP54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.83469315360056762</v>
       </c>
       <c r="AQ54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81322544272733299</v>
       </c>
       <c r="AR54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.80415729006277392</v>
       </c>
       <c r="AS54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.82126671198731027</v>
       </c>
       <c r="AT54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.83436106631249407</v>
       </c>
       <c r="AU54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.80498393189378137</v>
       </c>
       <c r="AV54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.7950981966072671</v>
       </c>
       <c r="AW54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.80465766185374943</v>
       </c>
       <c r="AX54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81440581362211462</v>
       </c>
       <c r="AY54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.80394329601467274</v>
       </c>
       <c r="AZ54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81432059703545756</v>
       </c>
       <c r="BA54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.80106859703550504</v>
       </c>
       <c r="BB54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81146981081642955</v>
       </c>
       <c r="BC54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.78482872294682526</v>
       </c>
       <c r="BD54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="BE54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="BF54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="BG54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.78999999999999992</v>
       </c>
       <c r="BH54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="BI54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="BJ54" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="216"/>
         <v>0.79</v>
       </c>
       <c r="BK54" s="10">
@@ -10145,85 +10174,85 @@
         <v>0.81785763269784661</v>
       </c>
       <c r="BL54" s="10">
-        <f t="shared" ref="BL54:BO54" si="215">+BL34/BL32</f>
+        <f t="shared" ref="BL54:BO54" si="217">+BL34/BL32</f>
         <v>0.81295590079598679</v>
       </c>
       <c r="BM54" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="217"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="BN54" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="217"/>
         <v>0.81731941717474421</v>
       </c>
       <c r="BO54" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="217"/>
         <v>0.82105213404546962</v>
       </c>
       <c r="BP54" s="10">
-        <f t="shared" ref="BP54:BR54" si="216">+BP34/BP32</f>
+        <f t="shared" ref="BP54:BR54" si="218">+BP34/BP32</f>
         <v>0.82130229817324696</v>
       </c>
       <c r="BQ54" s="10">
-        <f t="shared" si="216"/>
+        <f t="shared" si="218"/>
         <v>0.82034268763904605</v>
       </c>
       <c r="BR54" s="10">
-        <f t="shared" si="216"/>
-        <v>0.83</v>
+        <f t="shared" si="218"/>
+        <v>0.81791164390423077</v>
       </c>
       <c r="BS54" s="10"/>
       <c r="CI54" s="19">
-        <f t="shared" ref="CI54:CU54" si="217">+CI34/CI32</f>
+        <f t="shared" ref="CI54:CU54" si="219">+CI34/CI32</f>
         <v>0.8324617643898421</v>
       </c>
       <c r="CJ54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81936998741106415</v>
       </c>
       <c r="CK54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.80582795323678236</v>
       </c>
       <c r="CL54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="CM54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CN54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CO54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CP54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CQ54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CR54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CS54" s="19">
-        <f t="shared" si="217"/>
-        <v>0.80999999999999994</v>
+        <f t="shared" si="219"/>
+        <v>0.81</v>
       </c>
       <c r="CT54" s="19">
-        <f t="shared" si="217"/>
+        <f t="shared" si="219"/>
         <v>0.81</v>
       </c>
       <c r="CU54" s="19">
-        <f t="shared" si="217"/>
-        <v>0.81</v>
+        <f t="shared" si="219"/>
+        <v>0.81000000000000016</v>
       </c>
     </row>
     <row r="55" spans="2:106" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -10267,75 +10296,75 @@
       <c r="AK55" s="10"/>
       <c r="AL55" s="10"/>
       <c r="AM55" s="10">
-        <f t="shared" ref="AM55:AO55" si="218">+AM39/AM32</f>
+        <f t="shared" ref="AM55:AO55" si="220">+AM39/AM32</f>
         <v>0.45537355841551064</v>
       </c>
       <c r="AN55" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.44312599198851182</v>
       </c>
       <c r="AO55" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="220"/>
         <v>0.42114081736723247</v>
       </c>
       <c r="AP55" s="10">
-        <f t="shared" ref="AP55:AS55" si="219">+AP39/AP32</f>
+        <f t="shared" ref="AP55:AS55" si="221">+AP39/AP32</f>
         <v>0.46233889085964291</v>
       </c>
       <c r="AQ55" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="221"/>
         <v>0.41898255621144792</v>
       </c>
       <c r="AR55" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="221"/>
         <v>0.39239606774843067</v>
       </c>
       <c r="AS55" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="221"/>
         <v>0.40703602991162474</v>
       </c>
       <c r="AT55" s="10">
-        <f t="shared" ref="AT55:AV55" si="220">+AT39/AT32</f>
+        <f t="shared" ref="AT55:AV55" si="222">+AT39/AT32</f>
         <v>0.42016886443411439</v>
       </c>
       <c r="AU55" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="222"/>
         <v>0.33224333314540228</v>
       </c>
       <c r="AV55" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="222"/>
         <v>0.31909883876491679</v>
       </c>
       <c r="AW55" s="10">
-        <f t="shared" ref="AW55:AZ55" si="221">+AW39/AW32</f>
+        <f t="shared" ref="AW55:AZ55" si="223">+AW39/AW32</f>
         <v>0.37447601304145317</v>
       </c>
       <c r="AX55" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>0.45507979481333716</v>
       </c>
       <c r="AY55" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>0.43475602766420846</v>
       </c>
       <c r="AZ55" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="223"/>
         <v>0.42531898063761736</v>
       </c>
       <c r="BA55" s="10">
-        <f t="shared" ref="BA55:BD55" si="222">+BA39/BA32</f>
+        <f t="shared" ref="BA55:BD55" si="224">+BA39/BA32</f>
         <v>0.35928990003447087</v>
       </c>
       <c r="BB55" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="224"/>
         <v>0.37376377297971547</v>
       </c>
       <c r="BC55" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="224"/>
         <v>0.30543213415508097</v>
       </c>
       <c r="BD55" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="224"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="BE55" s="10">
@@ -10343,23 +10372,23 @@
         <v>0.20437324096124701</v>
       </c>
       <c r="BF55" s="10">
-        <f t="shared" ref="BF55:BJ55" si="223">+BF39/BF32</f>
+        <f t="shared" ref="BF55:BJ55" si="225">+BF39/BF32</f>
         <v>0.19894295041193844</v>
       </c>
       <c r="BG55" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="225"/>
         <v>0.36964391691394655</v>
       </c>
       <c r="BH55" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="225"/>
         <v>0.35194849839057468</v>
       </c>
       <c r="BI55" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="225"/>
         <v>0.40262402624026239</v>
       </c>
       <c r="BJ55" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="225"/>
         <v>0.39030914213058771</v>
       </c>
       <c r="BK55" s="10">
@@ -10367,92 +10396,92 @@
         <v>0.37904265532848719</v>
       </c>
       <c r="BL55" s="10">
-        <f t="shared" ref="BL55:BO55" si="224">+BL39/BL32</f>
+        <f t="shared" ref="BL55:BO55" si="226">+BL39/BL32</f>
         <v>0.38000051188861306</v>
       </c>
       <c r="BM55" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="226"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="BN55" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="226"/>
         <v>0.48289759222899659</v>
       </c>
       <c r="BO55" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="226"/>
         <v>0.41487450961856598</v>
       </c>
       <c r="BP55" s="10">
-        <f t="shared" ref="BP55:BR55" si="225">+BP39/BP32</f>
+        <f t="shared" ref="BP55:BR55" si="227">+BP39/BP32</f>
         <v>0.43019193534809325</v>
       </c>
       <c r="BQ55" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="227"/>
         <v>0.4007454822216151</v>
       </c>
       <c r="BR55" s="10">
-        <f t="shared" si="225"/>
-        <v>0.50074782608695656</v>
+        <f t="shared" si="227"/>
+        <v>0.41448225197849536</v>
       </c>
       <c r="BS55" s="10"/>
       <c r="CI55" s="10">
-        <f t="shared" ref="CI55:CU55" si="226">+CI39/CI32</f>
+        <f t="shared" ref="CI55:CU55" si="228">+CI39/CI32</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="CJ55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.41000325332050863</v>
       </c>
       <c r="CK55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.3800500203571221</v>
       </c>
       <c r="CL55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="CM55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.4149918959943058</v>
       </c>
       <c r="CN55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.48500203853196056</v>
       </c>
       <c r="CO55" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>0.55562009118541034</v>
       </c>
       <c r="CP55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.60831927210281411</v>
+        <f t="shared" si="228"/>
+        <v>0.61072178627230489</v>
       </c>
       <c r="CQ55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.6487212574867891</v>
+        <f t="shared" si="228"/>
+        <v>0.65064248450815898</v>
       </c>
       <c r="CR55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.678500792498126</v>
+        <f t="shared" si="228"/>
+        <v>0.68006727191633332</v>
       </c>
       <c r="CS55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.70250908147277236</v>
+        <f t="shared" si="228"/>
+        <v>0.70378956304156604</v>
       </c>
       <c r="CT55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.71962022653916158</v>
+        <f t="shared" si="228"/>
+        <v>0.72069687222880674</v>
       </c>
       <c r="CU55" s="10">
-        <f t="shared" si="226"/>
-        <v>0.73382761562387377</v>
+        <f t="shared" si="228"/>
+        <v>0.73473501631949611</v>
       </c>
       <c r="DA55" t="s">
         <v>112</v>
       </c>
       <c r="DB55" s="3">
-        <f>NPV(DB56,CN43:EY43)</f>
-        <v>3574567.6886036922</v>
+        <f>NPV(DB56,CQ43:EY43)</f>
+        <v>4309999.573098151</v>
       </c>
     </row>
     <row r="56" spans="2:106" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -10496,99 +10525,99 @@
       <c r="AK56" s="10"/>
       <c r="AL56" s="10"/>
       <c r="AM56" s="10">
-        <f t="shared" ref="AM56:BF56" si="227">+AM42/AM41</f>
+        <f t="shared" ref="AM56:BF56" si="229">+AM42/AM41</f>
         <v>0.11105169340463458</v>
       </c>
       <c r="AN56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.12985685071574643</v>
       </c>
       <c r="AO56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.13108930987821379</v>
       </c>
       <c r="AP56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.13662024840045164</v>
       </c>
       <c r="AQ56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.33972098727579336</v>
       </c>
       <c r="AR56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.32435597189695553</v>
       </c>
       <c r="AS56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.16891799699822621</v>
       </c>
       <c r="AT56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.19849492856363835</v>
       </c>
       <c r="AU56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.16362395495649207</v>
       </c>
       <c r="AV56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.15543956940140272</v>
       </c>
       <c r="AW56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>3.5288331488995447E-2</v>
       </c>
       <c r="AX56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.14063577173496744</v>
       </c>
       <c r="AY56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.17438928975049986</v>
       </c>
       <c r="AZ56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.16934388236234316</v>
       </c>
       <c r="BA56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.12976810222432561</v>
       </c>
       <c r="BB56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.19028499448905684</v>
       </c>
       <c r="BC56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.1619892231701841</v>
       </c>
       <c r="BD56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="BE56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="BF56" s="10">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="BG56" s="10">
-        <f t="shared" ref="BG56:BJ56" si="228">+BG42/BG41</f>
+        <f t="shared" ref="BG56:BJ56" si="230">+BG42/BG41</f>
         <v>0.19</v>
       </c>
       <c r="BH56" s="10">
-        <f t="shared" si="228"/>
+        <f t="shared" si="230"/>
         <v>0.13482038878437697</v>
       </c>
       <c r="BI56" s="10">
-        <f t="shared" si="228"/>
+        <f t="shared" si="230"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="BJ56" s="10">
-        <f t="shared" si="228"/>
+        <f t="shared" si="230"/>
         <v>0.17357299798690146</v>
       </c>
       <c r="BK56" s="10">
@@ -10596,84 +10625,84 @@
         <v>0.12789959811041388</v>
       </c>
       <c r="BL56" s="10">
-        <f t="shared" ref="BL56:BO56" si="229">+BL42/BL41</f>
+        <f t="shared" ref="BL56:BO56" si="231">+BL42/BL41</f>
         <v>0.10863233152389778</v>
       </c>
       <c r="BM56" s="10">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>0.11973964762652901</v>
       </c>
       <c r="BN56" s="10">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>0.11527193988027003</v>
       </c>
       <c r="BO56" s="10">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="BP56" s="10">
-        <f t="shared" ref="BP56:BR56" si="230">+BP42/BP41</f>
+        <f t="shared" ref="BP56:BR56" si="232">+BP42/BP41</f>
         <v>0.10699327943897925</v>
       </c>
       <c r="BQ56" s="10">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>0.87494806813460735</v>
       </c>
       <c r="BR56" s="10">
-        <f t="shared" si="230"/>
-        <v>0.15</v>
+        <f t="shared" si="232"/>
+        <v>0.10200457738142214</v>
       </c>
       <c r="BS56" s="10"/>
       <c r="CI56" s="19">
-        <f t="shared" ref="CI56:CU56" si="231">+CI42/CI41</f>
+        <f t="shared" ref="CI56:CU56" si="233">+CI42/CI41</f>
         <v>0.12814952091794488</v>
       </c>
       <c r="CJ56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.21222997450690997</v>
       </c>
       <c r="CK56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.12157926461723931</v>
       </c>
       <c r="CL56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.16737162676592504</v>
       </c>
       <c r="CM56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CN56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CO56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CP56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CQ56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CR56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CS56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CT56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="CU56" s="19">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>0.18</v>
       </c>
       <c r="DA56" s="3" t="s">
@@ -10697,63 +10726,63 @@
         <v>195</v>
       </c>
       <c r="BA58" s="6">
-        <f t="shared" ref="BA58:BC58" si="232">+BA59-BA73</f>
+        <f t="shared" ref="BA58:BC58" si="234">+BA59-BA73</f>
         <v>64833</v>
       </c>
       <c r="BB58" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>54773</v>
       </c>
       <c r="BC58" s="6">
-        <f t="shared" si="232"/>
+        <f t="shared" si="234"/>
         <v>50665</v>
       </c>
       <c r="BD58" s="6">
-        <f t="shared" ref="BD58:BG58" si="233">+BD59-BD73</f>
+        <f t="shared" ref="BD58:BG58" si="235">+BD59-BD73</f>
         <v>47025</v>
       </c>
       <c r="BE58" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>38382</v>
       </c>
       <c r="BF58" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>37016</v>
       </c>
       <c r="BG58" s="6">
-        <f t="shared" si="233"/>
+        <f t="shared" si="235"/>
         <v>33681</v>
       </c>
       <c r="BH58" s="6">
-        <f t="shared" ref="BH58:BO58" si="234">+BH59-BH73</f>
+        <f t="shared" ref="BH58:BO58" si="236">+BH59-BH73</f>
         <v>41272</v>
       </c>
       <c r="BI58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>48882</v>
       </c>
       <c r="BJ58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>53159</v>
       </c>
       <c r="BK58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>45951</v>
       </c>
       <c r="BL58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>45898</v>
       </c>
       <c r="BM58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>48148</v>
       </c>
       <c r="BN58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>55059</v>
       </c>
       <c r="BO58" s="6">
-        <f t="shared" si="234"/>
+        <f t="shared" si="236"/>
         <v>47569</v>
       </c>
       <c r="BP58" s="6"/>
@@ -10903,63 +10932,63 @@
         <v>46939</v>
       </c>
       <c r="CN59" s="3">
-        <f t="shared" ref="CN59:CU59" si="235">+CM59+CN43</f>
+        <f t="shared" ref="CN59:CU59" si="237">+CM59+CN43</f>
         <v>101359.15280000001</v>
       </c>
       <c r="CO59" s="3">
-        <f t="shared" si="235"/>
+        <f t="shared" si="237"/>
         <v>177969.03700592002</v>
       </c>
       <c r="CP59" s="3">
-        <f t="shared" si="235"/>
-        <v>279939.77230281709</v>
+        <f t="shared" si="237"/>
+        <v>281529.86710281717</v>
       </c>
       <c r="CQ59" s="3">
-        <f t="shared" si="235"/>
-        <v>411287.5760695833</v>
+        <f t="shared" si="237"/>
+        <v>414811.86218430335</v>
       </c>
       <c r="CR59" s="3">
-        <f t="shared" si="235"/>
-        <v>574471.85219442449</v>
+        <f t="shared" si="237"/>
+        <v>580305.51083822595</v>
       </c>
       <c r="CS59" s="3">
-        <f t="shared" si="235"/>
-        <v>775023.28126113501</v>
+        <f t="shared" si="237"/>
+        <v>783609.46950611891</v>
       </c>
       <c r="CT59" s="3">
-        <f t="shared" si="235"/>
-        <v>1012886.9674323954</v>
+        <f t="shared" si="237"/>
+        <v>1024669.3554039346</v>
       </c>
       <c r="CU59" s="3">
-        <f t="shared" si="235"/>
-        <v>1293536.569368474</v>
+        <f t="shared" si="237"/>
+        <v>1309025.8826779844</v>
       </c>
       <c r="CV59" s="3">
-        <f t="shared" ref="CV59" si="236">+CU59+CV43</f>
-        <v>1608716.6580969552</v>
+        <f t="shared" ref="CV59" si="238">+CU59+CV43</f>
+        <v>1628325.0597375038</v>
       </c>
       <c r="CW59" s="3">
-        <f t="shared" ref="CW59" si="237">+CV59+CW43</f>
-        <v>1955417.8586402927</v>
+        <f t="shared" ref="CW59" si="239">+CV59+CW43</f>
+        <v>1979522.1067479295</v>
       </c>
       <c r="CX59" s="3">
-        <f t="shared" ref="CX59" si="238">+CW59+CX43</f>
-        <v>2336138.4030969827</v>
+        <f t="shared" ref="CX59" si="240">+CW59+CX43</f>
+        <v>2365146.1710481825</v>
       </c>
       <c r="CY59" s="3">
-        <f t="shared" ref="CY59" si="239">+CX59+CY43</f>
-        <v>2742370.5869888104</v>
+        <f t="shared" ref="CY59" si="241">+CX59+CY43</f>
+        <v>2776587.7030177377</v>
       </c>
       <c r="CZ59" s="3">
-        <f t="shared" ref="CZ59" si="240">+CY59+CZ43</f>
-        <v>3175410.5437350851</v>
+        <f t="shared" ref="CZ59" si="242">+CY59+CZ43</f>
+        <v>3215159.1221843804</v>
       </c>
       <c r="DA59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="DB59" s="17">
+      <c r="DB59" s="26">
         <f>DB55/Main!M3</f>
-        <v>1380.1419647118503</v>
+        <v>1651.9737727474708</v>
       </c>
     </row>
     <row r="60" spans="2:106" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -11072,7 +11101,7 @@
       </c>
       <c r="DB60" s="19">
         <f>DB59/Main!M2-1</f>
-        <v>1.1286989507393388</v>
+        <v>1.497465867546746</v>
       </c>
     </row>
     <row r="61" spans="2:106" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -11670,23 +11699,23 @@
       <c r="AV66" s="6"/>
       <c r="AW66" s="6"/>
       <c r="AX66" s="6">
-        <f t="shared" ref="AX66:AY66" si="241">SUM(AX59:AX65)</f>
+        <f t="shared" ref="AX66:AY66" si="243">SUM(AX59:AX65)</f>
         <v>159316</v>
       </c>
       <c r="AY66" s="6">
-        <f t="shared" si="241"/>
+        <f t="shared" si="243"/>
         <v>163523</v>
       </c>
       <c r="AZ66" s="6">
-        <f t="shared" ref="AZ66:BA66" si="242">SUM(AZ59:AZ65)</f>
+        <f t="shared" ref="AZ66:BA66" si="244">SUM(AZ59:AZ65)</f>
         <v>170609</v>
       </c>
       <c r="BA66" s="6">
-        <f t="shared" si="242"/>
+        <f t="shared" si="244"/>
         <v>169585</v>
       </c>
       <c r="BB66" s="6">
-        <f t="shared" ref="BB66" si="243">SUM(BB59:BB65)</f>
+        <f t="shared" ref="BB66" si="245">SUM(BB59:BB65)</f>
         <v>165987</v>
       </c>
       <c r="BC66" s="6">
@@ -11702,43 +11731,43 @@
         <v>178894</v>
       </c>
       <c r="BF66" s="6">
-        <f t="shared" ref="BF66:BO66" si="244">SUM(BF59:BF65)</f>
+        <f t="shared" ref="BF66:BO66" si="246">SUM(BF59:BF65)</f>
         <v>185727</v>
       </c>
       <c r="BG66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>184491</v>
       </c>
       <c r="BH66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>206688</v>
       </c>
       <c r="BI66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>216274</v>
       </c>
       <c r="BJ66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>229623</v>
       </c>
       <c r="BK66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>222844</v>
       </c>
       <c r="BL66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>230238</v>
       </c>
       <c r="BM66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>256408</v>
       </c>
       <c r="BN66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>276054</v>
       </c>
       <c r="BO66" s="6">
-        <f t="shared" si="244"/>
+        <f t="shared" si="246"/>
         <v>280213</v>
       </c>
     </row>
@@ -12345,35 +12374,35 @@
         <v>61</v>
       </c>
       <c r="AX78" s="6">
-        <f t="shared" ref="AX78:AY78" si="245">SUM(AX68:AX77)</f>
+        <f t="shared" ref="AX78:AY78" si="247">SUM(AX68:AX77)</f>
         <v>159316</v>
       </c>
       <c r="AY78" s="6">
-        <f t="shared" si="245"/>
+        <f t="shared" si="247"/>
         <v>163523</v>
       </c>
       <c r="AZ78" s="6">
-        <f t="shared" ref="AZ78:BA78" si="246">SUM(AZ68:AZ77)</f>
+        <f t="shared" ref="AZ78:BA78" si="248">SUM(AZ68:AZ77)</f>
         <v>170609</v>
       </c>
       <c r="BA78" s="6">
-        <f t="shared" si="246"/>
+        <f t="shared" si="248"/>
         <v>169585</v>
       </c>
       <c r="BB78" s="6">
-        <f t="shared" ref="BB78:BE78" si="247">SUM(BB68:BB77)</f>
+        <f t="shared" ref="BB78:BE78" si="249">SUM(BB68:BB77)</f>
         <v>165987</v>
       </c>
       <c r="BC78" s="6">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>164218</v>
       </c>
       <c r="BD78" s="6">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>169779</v>
       </c>
       <c r="BE78" s="6">
-        <f t="shared" si="247"/>
+        <f t="shared" si="249"/>
         <v>178894</v>
       </c>
       <c r="BF78" s="6">
@@ -12397,23 +12426,23 @@
         <v>229623</v>
       </c>
       <c r="BK78" s="6">
-        <f t="shared" ref="BK78:BO78" si="248">SUM(BK68:BK77)</f>
+        <f t="shared" ref="BK78:BO78" si="250">SUM(BK68:BK77)</f>
         <v>222844</v>
       </c>
       <c r="BL78" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>230238</v>
       </c>
       <c r="BM78" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>256408</v>
       </c>
       <c r="BN78" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>276054</v>
       </c>
       <c r="BO78" s="6">
-        <f t="shared" si="248"/>
+        <f t="shared" si="250"/>
         <v>280213</v>
       </c>
     </row>
@@ -12425,31 +12454,31 @@
         <v>66</v>
       </c>
       <c r="AY80" s="6">
-        <f t="shared" ref="AY80:BJ80" si="249">AY43</f>
+        <f t="shared" ref="AY80:BJ80" si="251">AY43</f>
         <v>9497</v>
       </c>
       <c r="AZ80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>10394</v>
       </c>
       <c r="BA80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>9194</v>
       </c>
       <c r="BB80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>10285</v>
       </c>
       <c r="BC80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>7465</v>
       </c>
       <c r="BD80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>6687</v>
       </c>
       <c r="BE80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>4395</v>
       </c>
       <c r="BF80" s="6">
@@ -12457,39 +12486,39 @@
         <v>4652</v>
       </c>
       <c r="BG80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>8374.1444999999985</v>
       </c>
       <c r="BH80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>9658</v>
       </c>
       <c r="BI80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>11583</v>
       </c>
       <c r="BJ80" s="6">
-        <f t="shared" si="249"/>
+        <f t="shared" si="251"/>
         <v>13288.690000000002</v>
       </c>
       <c r="BK80" s="6">
-        <f t="shared" ref="BK80:BO80" si="250">BK43</f>
+        <f t="shared" ref="BK80:BO80" si="252">BK43</f>
         <v>12369</v>
       </c>
       <c r="BL80" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="252"/>
         <v>13465</v>
       </c>
       <c r="BM80" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="252"/>
         <v>15688</v>
       </c>
       <c r="BN80" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="252"/>
         <v>20838</v>
       </c>
       <c r="BO80" s="6">
-        <f t="shared" si="250"/>
+        <f t="shared" si="252"/>
         <v>16644</v>
       </c>
     </row>
@@ -12903,71 +12932,71 @@
         <v>68</v>
       </c>
       <c r="AY87" s="6">
-        <f t="shared" ref="AY87:BH87" si="251">SUM(AY81:AY86)</f>
+        <f t="shared" ref="AY87:BH87" si="253">SUM(AY81:AY86)</f>
         <v>12242</v>
       </c>
       <c r="AZ87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>13247</v>
       </c>
       <c r="BA87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>14090</v>
       </c>
       <c r="BB87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>18104</v>
       </c>
       <c r="BC87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>14076</v>
       </c>
       <c r="BD87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>12197</v>
       </c>
       <c r="BE87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>9691</v>
       </c>
       <c r="BF87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>14511</v>
       </c>
       <c r="BG87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>13998</v>
       </c>
       <c r="BH87" s="6">
-        <f t="shared" si="251"/>
+        <f t="shared" si="253"/>
         <v>17309</v>
       </c>
       <c r="BI87" s="6">
-        <f t="shared" ref="BI87:BO87" si="252">SUM(BI81:BI86)</f>
+        <f t="shared" ref="BI87:BO87" si="254">SUM(BI81:BI86)</f>
         <v>20402</v>
       </c>
       <c r="BJ87" s="6">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>19404</v>
       </c>
       <c r="BK87" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>19246</v>
       </c>
       <c r="BL87" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>19370</v>
       </c>
       <c r="BM87" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>24724</v>
       </c>
       <c r="BN87" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>27988</v>
       </c>
       <c r="BO87" s="3">
-        <f t="shared" si="252"/>
+        <f t="shared" si="254"/>
         <v>24026</v>
       </c>
       <c r="CA87" s="3">
@@ -13408,51 +13437,51 @@
       <c r="AW92" s="6"/>
       <c r="AX92" s="6"/>
       <c r="AY92" s="6">
-        <f t="shared" ref="AY92:BJ92" si="253">SUM(AY89:AY91)</f>
+        <f t="shared" ref="AY92:BJ92" si="255">SUM(AY89:AY91)</f>
         <v>-4874</v>
       </c>
       <c r="AZ92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-8195</v>
       </c>
       <c r="BA92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-330</v>
       </c>
       <c r="BB92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>5829</v>
       </c>
       <c r="BC92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-4779</v>
       </c>
       <c r="BD92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-6959</v>
       </c>
       <c r="BE92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-9701</v>
       </c>
       <c r="BF92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-7531</v>
       </c>
       <c r="BG92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-6743</v>
       </c>
       <c r="BH92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-5203</v>
       </c>
       <c r="BI92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-6077</v>
       </c>
       <c r="BJ92" s="6">
-        <f t="shared" si="253"/>
+        <f t="shared" si="255"/>
         <v>-6472</v>
       </c>
       <c r="BK92" s="3">
@@ -14126,71 +14155,71 @@
       <c r="AW99" s="6"/>
       <c r="AX99" s="6"/>
       <c r="AY99" s="6">
-        <f t="shared" ref="AY99:BA99" si="254">SUM(AY94:AY98)</f>
+        <f t="shared" ref="AY99:BA99" si="256">SUM(AY94:AY98)</f>
         <v>-5185</v>
       </c>
       <c r="AZ99" s="6">
-        <f t="shared" si="254"/>
+        <f t="shared" si="256"/>
         <v>-8549</v>
       </c>
       <c r="BA99" s="6">
-        <f t="shared" si="254"/>
+        <f t="shared" si="256"/>
         <v>-15252</v>
       </c>
       <c r="BB99" s="6">
-        <f t="shared" ref="BB99" si="255">SUM(BB94:BB98)</f>
+        <f t="shared" ref="BB99" si="257">SUM(BB94:BB98)</f>
         <v>-21742</v>
       </c>
       <c r="BC99" s="6">
-        <f t="shared" ref="BC99:BO99" si="256">SUM(BC94:BC98)</f>
+        <f t="shared" ref="BC99:BO99" si="258">SUM(BC94:BC98)</f>
         <v>-10660</v>
       </c>
       <c r="BD99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-6563</v>
       </c>
       <c r="BE99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>2147</v>
       </c>
       <c r="BF99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-7060</v>
       </c>
       <c r="BG99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-10516</v>
       </c>
       <c r="BH99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>5292</v>
       </c>
       <c r="BI99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-5875</v>
       </c>
       <c r="BJ99" s="6">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-8401</v>
       </c>
       <c r="BK99" s="3">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-19767</v>
       </c>
       <c r="BL99" s="3">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-11178</v>
       </c>
       <c r="BM99" s="3">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-4371</v>
       </c>
       <c r="BN99" s="3">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-5465</v>
       </c>
       <c r="BO99" s="3">
-        <f t="shared" si="256"/>
+        <f t="shared" si="258"/>
         <v>-19495</v>
       </c>
     </row>
@@ -14265,31 +14294,31 @@
         <v>81</v>
       </c>
       <c r="AY101" s="6">
-        <f t="shared" ref="AY101:BJ101" si="257">+AY100+AY99+AY92+AY87</f>
+        <f t="shared" ref="AY101:BJ101" si="259">+AY100+AY99+AY92+AY87</f>
         <v>1937</v>
       </c>
       <c r="AZ101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>-3380</v>
       </c>
       <c r="BA101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>-1707</v>
       </c>
       <c r="BB101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>2061</v>
       </c>
       <c r="BC101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>-1512</v>
       </c>
       <c r="BD101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>-1875</v>
       </c>
       <c r="BE101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>1773</v>
       </c>
       <c r="BF101" s="6">
@@ -14297,19 +14326,19 @@
         <v>345</v>
       </c>
       <c r="BG101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>-3176</v>
       </c>
       <c r="BH101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>17384</v>
       </c>
       <c r="BI101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>8096</v>
       </c>
       <c r="BJ101" s="6">
-        <f t="shared" si="257"/>
+        <f t="shared" si="259"/>
         <v>4927</v>
       </c>
       <c r="BK101" s="3">
@@ -14443,55 +14472,55 @@
         <v>199</v>
       </c>
       <c r="BC104" s="6">
-        <f t="shared" ref="BC104:BO104" si="258">+BC103-BB103</f>
+        <f t="shared" ref="BC104:BO104" si="260">+BC103-BB103</f>
         <v>5835</v>
       </c>
       <c r="BD104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>5748</v>
       </c>
       <c r="BE104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>3761</v>
       </c>
       <c r="BF104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>-1314</v>
       </c>
       <c r="BG104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>-8886</v>
       </c>
       <c r="BH104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>-5645</v>
       </c>
       <c r="BI104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>-5284</v>
       </c>
       <c r="BJ104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>1132</v>
       </c>
       <c r="BK104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>2012</v>
       </c>
       <c r="BL104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>1470</v>
       </c>
       <c r="BM104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>1605</v>
       </c>
       <c r="BN104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>1663</v>
       </c>
       <c r="BO104" s="6">
-        <f t="shared" si="258"/>
+        <f t="shared" si="260"/>
         <v>2767</v>
       </c>
     </row>
@@ -14508,51 +14537,51 @@
         <v>7970</v>
       </c>
       <c r="AZ106" s="6">
-        <f t="shared" ref="AZ106:BC106" si="259">+AZ87+AZ89</f>
+        <f t="shared" ref="AZ106:BC106" si="261">+AZ87+AZ89</f>
         <v>8635</v>
       </c>
       <c r="BA106" s="6">
-        <f t="shared" si="259"/>
+        <f t="shared" si="261"/>
         <v>9776</v>
       </c>
       <c r="BB106" s="6">
-        <f t="shared" si="259"/>
+        <f t="shared" si="261"/>
         <v>12734</v>
       </c>
       <c r="BC106" s="6">
-        <f t="shared" si="259"/>
+        <f t="shared" si="261"/>
         <v>8761</v>
       </c>
       <c r="BD106" s="6">
-        <f t="shared" ref="BD106:BJ106" si="260">+BD87+BD89</f>
+        <f t="shared" ref="BD106:BJ106" si="262">+BD87+BD89</f>
         <v>4669</v>
       </c>
       <c r="BE106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>336</v>
       </c>
       <c r="BF106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>5523</v>
       </c>
       <c r="BG106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>7175</v>
       </c>
       <c r="BH106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>11175</v>
       </c>
       <c r="BI106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>13906</v>
       </c>
       <c r="BJ106" s="6">
-        <f t="shared" si="260"/>
+        <f t="shared" si="262"/>
         <v>11812</v>
       </c>
       <c r="BK106" s="3">
-        <f t="shared" ref="BK106" si="261">+BK87+BK89</f>
+        <f t="shared" ref="BK106" si="263">+BK87+BK89</f>
         <v>12846</v>
       </c>
       <c r="BL106" s="3">
@@ -14577,11 +14606,11 @@
         <v>127</v>
       </c>
       <c r="BB107" s="6">
-        <f t="shared" ref="BB107:BC107" si="262">SUM(AY106:BB106)</f>
+        <f t="shared" ref="BB107:BC107" si="264">SUM(AY106:BB106)</f>
         <v>39115</v>
       </c>
       <c r="BC107" s="6">
-        <f t="shared" si="262"/>
+        <f t="shared" si="264"/>
         <v>39906</v>
       </c>
       <c r="BD107" s="6">
@@ -14597,31 +14626,31 @@
         <v>19289</v>
       </c>
       <c r="BG107" s="6">
-        <f t="shared" ref="BG107:BK107" si="263">SUM(BD106:BG106)</f>
+        <f t="shared" ref="BG107:BK107" si="265">SUM(BD106:BG106)</f>
         <v>17703</v>
       </c>
       <c r="BH107" s="6">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>24209</v>
       </c>
       <c r="BI107" s="6">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>37779</v>
       </c>
       <c r="BJ107" s="6">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>44068</v>
       </c>
       <c r="BK107" s="6">
-        <f t="shared" si="263"/>
+        <f t="shared" si="265"/>
         <v>49739</v>
       </c>
       <c r="BL107" s="3">
-        <f t="shared" ref="BL107:BM107" si="264">SUM(BI106:BL106)</f>
+        <f t="shared" ref="BL107:BM107" si="266">SUM(BI106:BL106)</f>
         <v>49761</v>
       </c>
       <c r="BM107" s="3">
-        <f t="shared" si="264"/>
+        <f t="shared" si="266"/>
         <v>52321</v>
       </c>
       <c r="BN107" s="3">
@@ -14680,59 +14709,59 @@
         <v>94400</v>
       </c>
       <c r="AZ110" s="3">
-        <f t="shared" ref="AZ110:BM110" si="265">SUM(AW32:AZ32)</f>
+        <f t="shared" ref="AZ110:BM110" si="267">SUM(AW32:AZ32)</f>
         <v>104790</v>
       </c>
       <c r="BA110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>112330</v>
       </c>
       <c r="BB110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>117929</v>
       </c>
       <c r="BC110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>119666</v>
       </c>
       <c r="BD110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>119411</v>
       </c>
       <c r="BE110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>118115</v>
       </c>
       <c r="BF110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>116609</v>
       </c>
       <c r="BG110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>117346</v>
       </c>
       <c r="BH110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>120523</v>
       </c>
       <c r="BI110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>126955</v>
       </c>
       <c r="BJ110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>134901</v>
       </c>
       <c r="BK110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>142711</v>
       </c>
       <c r="BL110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>149783</v>
       </c>
       <c r="BM110" s="3">
-        <f t="shared" si="265"/>
+        <f t="shared" si="267"/>
         <v>156226</v>
       </c>
       <c r="BN110" s="3">
@@ -14753,7 +14782,7 @@
       </c>
       <c r="BR110" s="3">
         <f>SUM(BO32:BR32)</f>
-        <v>198572</v>
+        <v>200966</v>
       </c>
     </row>
     <row r="111" spans="2:70" x14ac:dyDescent="0.2">
